--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_chemical_diversified.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_chemical_diversified.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0894288477532605</v>
+        <v>0.08928599005775398</v>
       </c>
       <c r="C2">
-        <v>306.1442815089868</v>
+        <v>303.9664903334826</v>
       </c>
       <c r="D2">
-        <v>289.2442815089868</v>
+        <v>290.1944903334826</v>
       </c>
       <c r="E2">
-        <v>-86.8</v>
+        <v>-83.672</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.128</v>
       </c>
       <c r="G2">
         <v>16.9</v>
@@ -1579,28 +1579,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1573384</v>
       </c>
       <c r="N2">
-        <v>20.42040816326531</v>
+        <v>20.26306976326531</v>
       </c>
       <c r="O2">
-        <v>4.084081632653062</v>
+        <v>4.052613952653061</v>
       </c>
       <c r="P2">
-        <v>16.33632653061225</v>
+        <v>16.21045581061225</v>
       </c>
       <c r="Q2">
-        <v>26.93632653061225</v>
+        <v>26.81045581061224</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0894288477532605</v>
+        <v>0.0897814040987414</v>
       </c>
       <c r="T2">
-        <v>0.8504074490426663</v>
+        <v>0.8572794284288697</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>129.786550284389</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08928599005775398</v>
+        <v>0.08914313236224745</v>
       </c>
       <c r="C3">
-        <v>303.9664903334826</v>
+        <v>301.7949628789196</v>
       </c>
       <c r="D3">
-        <v>290.1944903334826</v>
+        <v>291.1509628789196</v>
       </c>
       <c r="E3">
-        <v>-83.672</v>
+        <v>-80.544</v>
       </c>
       <c r="F3">
-        <v>3.128</v>
+        <v>6.256</v>
       </c>
       <c r="G3">
         <v>16.9</v>
@@ -1661,28 +1661,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M3">
-        <v>0.1573384</v>
+        <v>0.3146768</v>
       </c>
       <c r="N3">
-        <v>20.26306976326531</v>
+        <v>20.10573136326531</v>
       </c>
       <c r="O3">
-        <v>4.052613952653061</v>
+        <v>4.021146272653062</v>
       </c>
       <c r="P3">
-        <v>16.21045581061225</v>
+        <v>16.08458509061224</v>
       </c>
       <c r="Q3">
-        <v>26.81045581061224</v>
+        <v>26.68458509061224</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0897814040987414</v>
+        <v>0.09014115547168108</v>
       </c>
       <c r="T3">
-        <v>0.8572794284288697</v>
+        <v>0.8642916522923425</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>129.786550284389</v>
+        <v>64.89327514219448</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08914313236224745</v>
+        <v>0.08900027466674093</v>
       </c>
       <c r="C4">
-        <v>301.7949628789196</v>
+        <v>299.6297612852318</v>
       </c>
       <c r="D4">
-        <v>291.1509628789196</v>
+        <v>292.1137612852318</v>
       </c>
       <c r="E4">
-        <v>-80.544</v>
+        <v>-77.416</v>
       </c>
       <c r="F4">
-        <v>6.256</v>
+        <v>9.384</v>
       </c>
       <c r="G4">
         <v>16.9</v>
@@ -1743,28 +1743,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M4">
-        <v>0.3146768</v>
+        <v>0.4720152</v>
       </c>
       <c r="N4">
-        <v>20.10573136326531</v>
+        <v>19.94839296326531</v>
       </c>
       <c r="O4">
-        <v>4.021146272653062</v>
+        <v>3.989678592653061</v>
       </c>
       <c r="P4">
-        <v>16.08458509061224</v>
+        <v>15.95871437061225</v>
       </c>
       <c r="Q4">
-        <v>26.68458509061224</v>
+        <v>26.55871437061224</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09014115547168108</v>
+        <v>0.09050832439870199</v>
       </c>
       <c r="T4">
-        <v>0.8642916522923425</v>
+        <v>0.8714484580911446</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>64.89327514219448</v>
+        <v>43.26218342812966</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08900027466674093</v>
+        <v>0.08885741697123442</v>
       </c>
       <c r="C5">
-        <v>299.6297612852318</v>
+        <v>297.470948517035</v>
       </c>
       <c r="D5">
-        <v>292.1137612852318</v>
+        <v>293.082948517035</v>
       </c>
       <c r="E5">
-        <v>-77.416</v>
+        <v>-74.288</v>
       </c>
       <c r="F5">
-        <v>9.384</v>
+        <v>12.512</v>
       </c>
       <c r="G5">
         <v>16.9</v>
@@ -1825,28 +1825,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M5">
-        <v>0.4720152</v>
+        <v>0.6293536</v>
       </c>
       <c r="N5">
-        <v>19.94839296326531</v>
+        <v>19.79105456326531</v>
       </c>
       <c r="O5">
-        <v>3.989678592653061</v>
+        <v>3.958210912653061</v>
       </c>
       <c r="P5">
-        <v>15.95871437061225</v>
+        <v>15.83284365061224</v>
       </c>
       <c r="Q5">
-        <v>26.55871437061224</v>
+        <v>26.43284365061224</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09050832439870199</v>
+        <v>0.09088314267836919</v>
       </c>
       <c r="T5">
-        <v>0.8714484580911446</v>
+        <v>0.8787543640107552</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.26218342812966</v>
+        <v>32.44663757109724</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08885741697123442</v>
+        <v>0.0887145592757279</v>
       </c>
       <c r="C6">
-        <v>297.470948517035</v>
+        <v>295.3185883773535</v>
       </c>
       <c r="D6">
-        <v>293.082948517035</v>
+        <v>294.0585883773535</v>
       </c>
       <c r="E6">
-        <v>-74.288</v>
+        <v>-71.16</v>
       </c>
       <c r="F6">
-        <v>12.512</v>
+        <v>15.64</v>
       </c>
       <c r="G6">
         <v>16.9</v>
@@ -1907,28 +1907,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M6">
-        <v>0.6293536</v>
+        <v>0.7866919999999999</v>
       </c>
       <c r="N6">
-        <v>19.79105456326531</v>
+        <v>19.63371616326531</v>
       </c>
       <c r="O6">
-        <v>3.958210912653061</v>
+        <v>3.926743232653062</v>
       </c>
       <c r="P6">
-        <v>15.83284365061224</v>
+        <v>15.70697293061225</v>
       </c>
       <c r="Q6">
-        <v>26.43284365061224</v>
+        <v>26.30697293061225</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09088314267836919</v>
+        <v>0.09126585186918726</v>
       </c>
       <c r="T6">
-        <v>0.8787543640107552</v>
+        <v>0.8862140784760416</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.44663757109724</v>
+        <v>25.9573100568778</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0887145592757279</v>
+        <v>0.08857170158022137</v>
       </c>
       <c r="C7">
-        <v>295.3185883773535</v>
+        <v>293.1727455216209</v>
       </c>
       <c r="D7">
-        <v>294.0585883773535</v>
+        <v>295.0407455216209</v>
       </c>
       <c r="E7">
-        <v>-71.16</v>
+        <v>-68.032</v>
       </c>
       <c r="F7">
-        <v>15.64</v>
+        <v>18.768</v>
       </c>
       <c r="G7">
         <v>16.9</v>
@@ -1989,28 +1989,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M7">
-        <v>0.7866919999999999</v>
+        <v>0.9440303999999999</v>
       </c>
       <c r="N7">
-        <v>19.63371616326531</v>
+        <v>19.47637776326531</v>
       </c>
       <c r="O7">
-        <v>3.926743232653062</v>
+        <v>3.895275552653062</v>
       </c>
       <c r="P7">
-        <v>15.70697293061225</v>
+        <v>15.58110221061225</v>
       </c>
       <c r="Q7">
-        <v>26.30697293061225</v>
+        <v>26.18110221061225</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09126585186918726</v>
+        <v>0.09165670380874615</v>
       </c>
       <c r="T7">
-        <v>0.8862140784760416</v>
+        <v>0.893832510270377</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>25.9573100568778</v>
+        <v>21.63109171406483</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08857170158022137</v>
+        <v>0.08842884388471485</v>
       </c>
       <c r="C8">
-        <v>293.1727455216209</v>
+        <v>291.0334854719638</v>
       </c>
       <c r="D8">
-        <v>295.0407455216209</v>
+        <v>296.0294854719638</v>
       </c>
       <c r="E8">
-        <v>-68.032</v>
+        <v>-64.904</v>
       </c>
       <c r="F8">
-        <v>18.768</v>
+        <v>21.896</v>
       </c>
       <c r="G8">
         <v>16.9</v>
@@ -2071,28 +2071,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M8">
-        <v>0.9440303999999999</v>
+        <v>1.1013688</v>
       </c>
       <c r="N8">
-        <v>19.47637776326531</v>
+        <v>19.31903936326531</v>
       </c>
       <c r="O8">
-        <v>3.895275552653062</v>
+        <v>3.863807872653062</v>
       </c>
       <c r="P8">
-        <v>15.58110221061225</v>
+        <v>15.45523149061225</v>
       </c>
       <c r="Q8">
-        <v>26.18110221061225</v>
+        <v>26.05523149061224</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09165670380874615</v>
+        <v>0.09205596116636006</v>
       </c>
       <c r="T8">
-        <v>0.893832510270377</v>
+        <v>0.9016147793076011</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.63109171406483</v>
+        <v>18.54093575491272</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08842884388471484</v>
+        <v>0.08828598618920834</v>
       </c>
       <c r="C9">
-        <v>291.0334854719638</v>
+        <v>288.9008746317721</v>
       </c>
       <c r="D9">
-        <v>296.0294854719639</v>
+        <v>297.0248746317721</v>
       </c>
       <c r="E9">
-        <v>-64.904</v>
+        <v>-61.776</v>
       </c>
       <c r="F9">
-        <v>21.896</v>
+        <v>25.024</v>
       </c>
       <c r="G9">
         <v>16.9</v>
@@ -2153,28 +2153,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M9">
-        <v>1.1013688</v>
+        <v>1.2587072</v>
       </c>
       <c r="N9">
-        <v>19.31903936326531</v>
+        <v>19.16170096326531</v>
       </c>
       <c r="O9">
-        <v>3.863807872653062</v>
+        <v>3.832340192653062</v>
       </c>
       <c r="P9">
-        <v>15.45523149061225</v>
+        <v>15.32936077061225</v>
       </c>
       <c r="Q9">
-        <v>26.05523149061224</v>
+        <v>25.92936077061224</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09205596116636006</v>
+        <v>0.09246389803174819</v>
       </c>
       <c r="T9">
-        <v>0.9016147793076011</v>
+        <v>0.909566228106504</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.54093575491271</v>
+        <v>16.22331878554862</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08828598618920834</v>
+        <v>0.0881431284937018</v>
       </c>
       <c r="C10">
-        <v>288.9008746317721</v>
+        <v>286.7749803005661</v>
       </c>
       <c r="D10">
-        <v>297.0248746317721</v>
+        <v>298.0269803005661</v>
       </c>
       <c r="E10">
-        <v>-61.776</v>
+        <v>-58.648</v>
       </c>
       <c r="F10">
-        <v>25.024</v>
+        <v>28.152</v>
       </c>
       <c r="G10">
         <v>16.9</v>
@@ -2235,28 +2235,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M10">
-        <v>1.2587072</v>
+        <v>1.4160456</v>
       </c>
       <c r="N10">
-        <v>19.16170096326531</v>
+        <v>19.00436256326531</v>
       </c>
       <c r="O10">
-        <v>3.832340192653062</v>
+        <v>3.800872512653061</v>
       </c>
       <c r="P10">
-        <v>15.32936077061225</v>
+        <v>15.20349005061225</v>
       </c>
       <c r="Q10">
-        <v>25.92936077061224</v>
+        <v>25.80349005061224</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09246389803174819</v>
+        <v>0.09288080054252945</v>
       </c>
       <c r="T10">
-        <v>0.909566228106504</v>
+        <v>0.9176924340218662</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.22331878554862</v>
+        <v>14.42072780937655</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0881431284937018</v>
+        <v>0.08800027079819529</v>
       </c>
       <c r="C11">
-        <v>286.7749803005661</v>
+        <v>284.6558706891634</v>
       </c>
       <c r="D11">
-        <v>298.0269803005661</v>
+        <v>299.0358706891634</v>
       </c>
       <c r="E11">
-        <v>-58.648</v>
+        <v>-55.52</v>
       </c>
       <c r="F11">
-        <v>28.152</v>
+        <v>31.28</v>
       </c>
       <c r="G11">
         <v>16.9</v>
@@ -2317,28 +2317,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M11">
-        <v>1.4160456</v>
+        <v>1.573384</v>
       </c>
       <c r="N11">
-        <v>19.00436256326531</v>
+        <v>18.84702416326531</v>
       </c>
       <c r="O11">
-        <v>3.800872512653061</v>
+        <v>3.769404832653061</v>
       </c>
       <c r="P11">
-        <v>15.20349005061225</v>
+        <v>15.07761933061225</v>
       </c>
       <c r="Q11">
-        <v>25.80349005061224</v>
+        <v>25.67761933061225</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09288080054252945</v>
+        <v>0.09330696755355032</v>
       </c>
       <c r="T11">
-        <v>0.9176924340218662</v>
+        <v>0.9259992222909033</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.42072780937655</v>
+        <v>12.9786550284389</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08800027079819531</v>
+        <v>0.08798941310268876</v>
       </c>
       <c r="C12">
-        <v>284.6558706891633</v>
+        <v>281.6048293427851</v>
       </c>
       <c r="D12">
-        <v>299.0358706891633</v>
+        <v>299.1128293427852</v>
       </c>
       <c r="E12">
-        <v>-55.52</v>
+        <v>-52.392</v>
       </c>
       <c r="F12">
-        <v>31.28</v>
+        <v>34.408</v>
       </c>
       <c r="G12">
         <v>16.9</v>
@@ -2399,45 +2399,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M12">
-        <v>1.573384</v>
+        <v>1.7823344</v>
       </c>
       <c r="N12">
-        <v>18.84702416326531</v>
+        <v>18.63807376326531</v>
       </c>
       <c r="O12">
-        <v>3.769404832653061</v>
+        <v>3.727614752653062</v>
       </c>
       <c r="P12">
-        <v>15.07761933061225</v>
+        <v>14.91045901061225</v>
       </c>
       <c r="Q12">
-        <v>25.67761933061225</v>
+        <v>25.51045901061224</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09330696755355034</v>
+        <v>0.09374271135133569</v>
       </c>
       <c r="T12">
-        <v>0.9259992222909034</v>
+        <v>0.9344926799592445</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>12.9786550284389</v>
+        <v>11.45711386329373</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08798941310268876</v>
+        <v>0.08785855540718225</v>
       </c>
       <c r="C13">
-        <v>281.6048293427851</v>
+        <v>279.4074655751828</v>
       </c>
       <c r="D13">
-        <v>299.1128293427852</v>
+        <v>300.0434655751828</v>
       </c>
       <c r="E13">
-        <v>-52.392</v>
+        <v>-49.264</v>
       </c>
       <c r="F13">
-        <v>34.408</v>
+        <v>37.536</v>
       </c>
       <c r="G13">
         <v>16.9</v>
@@ -2481,28 +2481,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M13">
-        <v>1.7823344</v>
+        <v>1.9443648</v>
       </c>
       <c r="N13">
-        <v>18.63807376326531</v>
+        <v>18.47604336326531</v>
       </c>
       <c r="O13">
-        <v>3.727614752653062</v>
+        <v>3.695208672653062</v>
       </c>
       <c r="P13">
-        <v>14.91045901061225</v>
+        <v>14.78083469061225</v>
       </c>
       <c r="Q13">
-        <v>25.51045901061224</v>
+        <v>25.38083469061225</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09374271135133569</v>
+        <v>0.09418835841725257</v>
       </c>
       <c r="T13">
-        <v>0.9344926799592445</v>
+        <v>0.9431791707564118</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.45711386329373</v>
+        <v>10.50235437468592</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08785855540718225</v>
+        <v>0.08790449771167573</v>
       </c>
       <c r="C14">
-        <v>279.4074655751828</v>
+        <v>275.952073277307</v>
       </c>
       <c r="D14">
-        <v>300.0434655751828</v>
+        <v>299.716073277307</v>
       </c>
       <c r="E14">
-        <v>-49.264</v>
+        <v>-46.136</v>
       </c>
       <c r="F14">
-        <v>37.536</v>
+        <v>40.664</v>
       </c>
       <c r="G14">
         <v>16.9</v>
@@ -2563,45 +2563,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M14">
-        <v>1.9443648</v>
+        <v>2.175524</v>
       </c>
       <c r="N14">
-        <v>18.47604336326531</v>
+        <v>18.24488416326531</v>
       </c>
       <c r="O14">
-        <v>3.695208672653062</v>
+        <v>3.648976832653062</v>
       </c>
       <c r="P14">
-        <v>14.78083469061225</v>
+        <v>14.59590733061225</v>
       </c>
       <c r="Q14">
-        <v>25.38083469061225</v>
+        <v>25.19590733061224</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09418835841725257</v>
+        <v>0.09464425024330543</v>
       </c>
       <c r="T14">
-        <v>0.9431791707564118</v>
+        <v>0.9520653509971919</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.50235437468592</v>
+        <v>9.38643203350793</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08790449771167573</v>
+        <v>0.08778724001616921</v>
       </c>
       <c r="C15">
-        <v>275.952073277307</v>
+        <v>273.6610898577068</v>
       </c>
       <c r="D15">
-        <v>299.716073277307</v>
+        <v>300.5530898577068</v>
       </c>
       <c r="E15">
-        <v>-46.136</v>
+        <v>-43.00799999999999</v>
       </c>
       <c r="F15">
-        <v>40.664</v>
+        <v>43.79200000000001</v>
       </c>
       <c r="G15">
         <v>16.9</v>
@@ -2645,28 +2645,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M15">
-        <v>2.175524</v>
+        <v>2.342872</v>
       </c>
       <c r="N15">
-        <v>18.24488416326531</v>
+        <v>18.07753616326531</v>
       </c>
       <c r="O15">
-        <v>3.648976832653062</v>
+        <v>3.615507232653062</v>
       </c>
       <c r="P15">
-        <v>14.59590733061225</v>
+        <v>14.46202893061225</v>
       </c>
       <c r="Q15">
-        <v>25.19590733061224</v>
+        <v>25.06202893061224</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09464425024330543</v>
+        <v>0.09511074420484791</v>
       </c>
       <c r="T15">
-        <v>0.9520653509971919</v>
+        <v>0.9611581865924089</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.38643203350793</v>
+        <v>8.715972602543077</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08778724001616921</v>
+        <v>0.08766998232066267</v>
       </c>
       <c r="C16">
-        <v>273.6610898577068</v>
+        <v>271.3747946003594</v>
       </c>
       <c r="D16">
-        <v>300.5530898577068</v>
+        <v>301.3947946003594</v>
       </c>
       <c r="E16">
-        <v>-43.00799999999999</v>
+        <v>-39.87999999999999</v>
       </c>
       <c r="F16">
-        <v>43.79200000000001</v>
+        <v>46.92000000000001</v>
       </c>
       <c r="G16">
         <v>16.9</v>
@@ -2727,28 +2727,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M16">
-        <v>2.342872</v>
+        <v>2.51022</v>
       </c>
       <c r="N16">
-        <v>18.07753616326531</v>
+        <v>17.91018816326531</v>
       </c>
       <c r="O16">
-        <v>3.615507232653062</v>
+        <v>3.582037632653062</v>
       </c>
       <c r="P16">
-        <v>14.46202893061225</v>
+        <v>14.32815053061224</v>
       </c>
       <c r="Q16">
-        <v>25.06202893061224</v>
+        <v>24.92815053061224</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09511074420484791</v>
+        <v>0.09558821449489727</v>
       </c>
       <c r="T16">
-        <v>0.9611581865924089</v>
+        <v>0.9704649712604544</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.715972602543077</v>
+        <v>8.134907762373539</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08766998232066267</v>
+        <v>0.08755272462515618</v>
       </c>
       <c r="C17">
-        <v>271.3747946003594</v>
+        <v>269.093227003748</v>
       </c>
       <c r="D17">
-        <v>301.3947946003594</v>
+        <v>302.241227003748</v>
       </c>
       <c r="E17">
-        <v>-39.88</v>
+        <v>-36.752</v>
       </c>
       <c r="F17">
-        <v>46.92</v>
+        <v>50.048</v>
       </c>
       <c r="G17">
         <v>16.9</v>
@@ -2809,28 +2809,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M17">
-        <v>2.51022</v>
+        <v>2.677568</v>
       </c>
       <c r="N17">
-        <v>17.91018816326531</v>
+        <v>17.74284016326531</v>
       </c>
       <c r="O17">
-        <v>3.582037632653062</v>
+        <v>3.548568032653062</v>
       </c>
       <c r="P17">
-        <v>14.32815053061224</v>
+        <v>14.19427213061224</v>
       </c>
       <c r="Q17">
-        <v>24.92815053061224</v>
+        <v>24.79427213061224</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09558821449489727</v>
+        <v>0.09607705312518591</v>
       </c>
       <c r="T17">
-        <v>0.9704649712604544</v>
+        <v>0.9799933460396439</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.13490776237354</v>
+        <v>7.626476027225193</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08755272462515618</v>
+        <v>0.08754426692964963</v>
       </c>
       <c r="C18">
-        <v>269.093227003748</v>
+        <v>266.0264632993052</v>
       </c>
       <c r="D18">
-        <v>302.241227003748</v>
+        <v>302.3024632993053</v>
       </c>
       <c r="E18">
-        <v>-36.752</v>
+        <v>-33.62399999999999</v>
       </c>
       <c r="F18">
-        <v>50.048</v>
+        <v>53.17600000000001</v>
       </c>
       <c r="G18">
         <v>16.9</v>
@@ -2891,45 +2891,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M18">
-        <v>2.677568</v>
+        <v>2.887456800000001</v>
       </c>
       <c r="N18">
-        <v>17.74284016326531</v>
+        <v>17.5329513632653</v>
       </c>
       <c r="O18">
-        <v>3.548568032653062</v>
+        <v>3.506590272653061</v>
       </c>
       <c r="P18">
-        <v>14.19427213061224</v>
+        <v>14.02636109061224</v>
       </c>
       <c r="Q18">
-        <v>24.79427213061224</v>
+        <v>24.62636109061224</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09607705312518591</v>
+        <v>0.09657767099957788</v>
       </c>
       <c r="T18">
-        <v>0.9799933460396439</v>
+        <v>0.9897513202111031</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.626476027225193</v>
+        <v>7.072108633197664</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08754426692964963</v>
+        <v>0.08743340923414313</v>
       </c>
       <c r="C19">
-        <v>266.0264632993052</v>
+        <v>263.7034070942951</v>
       </c>
       <c r="D19">
-        <v>302.3024632993053</v>
+        <v>303.1074070942951</v>
       </c>
       <c r="E19">
-        <v>-33.62399999999999</v>
+        <v>-30.49599999999999</v>
       </c>
       <c r="F19">
-        <v>53.17600000000001</v>
+        <v>56.30400000000001</v>
       </c>
       <c r="G19">
         <v>16.9</v>
@@ -2973,28 +2973,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M19">
-        <v>2.887456800000001</v>
+        <v>3.0573072</v>
       </c>
       <c r="N19">
-        <v>17.5329513632653</v>
+        <v>17.36310096326531</v>
       </c>
       <c r="O19">
-        <v>3.506590272653061</v>
+        <v>3.472620192653062</v>
       </c>
       <c r="P19">
-        <v>14.02636109061224</v>
+        <v>13.89048077061225</v>
       </c>
       <c r="Q19">
-        <v>24.62636109061224</v>
+        <v>24.49048077061224</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09657767099957788</v>
+        <v>0.09709049906602821</v>
       </c>
       <c r="T19">
-        <v>0.9897513202111031</v>
+        <v>0.9997472937525981</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.072108633197664</v>
+        <v>6.679213709131129</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08743340923414313</v>
+        <v>0.08732255153863661</v>
       </c>
       <c r="C20">
-        <v>263.7034070942951</v>
+        <v>261.3846489977018</v>
       </c>
       <c r="D20">
-        <v>303.1074070942951</v>
+        <v>303.9166489977019</v>
       </c>
       <c r="E20">
-        <v>-30.496</v>
+        <v>-27.36799999999999</v>
       </c>
       <c r="F20">
-        <v>56.304</v>
+        <v>59.432</v>
       </c>
       <c r="G20">
         <v>16.9</v>
@@ -3055,28 +3055,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M20">
-        <v>3.0573072</v>
+        <v>3.2271576</v>
       </c>
       <c r="N20">
-        <v>17.36310096326531</v>
+        <v>17.19325056326531</v>
       </c>
       <c r="O20">
-        <v>3.472620192653062</v>
+        <v>3.438650112653062</v>
       </c>
       <c r="P20">
-        <v>13.89048077061225</v>
+        <v>13.75460045061225</v>
       </c>
       <c r="Q20">
-        <v>24.49048077061224</v>
+        <v>24.35460045061225</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09709049906602819</v>
+        <v>0.09761598955387235</v>
       </c>
       <c r="T20">
-        <v>0.9997472937525979</v>
+        <v>1.009990081455611</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.679213709131129</v>
+        <v>6.327676145492649</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08732255153863661</v>
+        <v>0.08737169384313007</v>
       </c>
       <c r="C21">
-        <v>261.3846489977018</v>
+        <v>257.89738616463</v>
       </c>
       <c r="D21">
-        <v>303.9166489977019</v>
+        <v>303.55738616463</v>
       </c>
       <c r="E21">
-        <v>-27.36799999999999</v>
+        <v>-24.23999999999999</v>
       </c>
       <c r="F21">
-        <v>59.432</v>
+        <v>62.56</v>
       </c>
       <c r="G21">
         <v>16.9</v>
@@ -3137,45 +3137,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M21">
-        <v>3.2271576</v>
+        <v>3.459568</v>
       </c>
       <c r="N21">
-        <v>17.19325056326531</v>
+        <v>16.96084016326531</v>
       </c>
       <c r="O21">
-        <v>3.438650112653062</v>
+        <v>3.392168032653061</v>
       </c>
       <c r="P21">
-        <v>13.75460045061225</v>
+        <v>13.56867213061225</v>
       </c>
       <c r="Q21">
-        <v>24.35460045061225</v>
+        <v>24.16867213061224</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09761598955387235</v>
+        <v>0.09815461730391259</v>
       </c>
       <c r="T21">
-        <v>1.009990081455611</v>
+        <v>1.0204889388512</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.327676145492649</v>
+        <v>5.902589040962717</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08737169384313007</v>
+        <v>0.08726883614762358</v>
       </c>
       <c r="C22">
-        <v>257.89738616463</v>
+        <v>255.5223181515253</v>
       </c>
       <c r="D22">
-        <v>303.55738616463</v>
+        <v>304.3103181515253</v>
       </c>
       <c r="E22">
-        <v>-24.23999999999999</v>
+        <v>-21.11199999999999</v>
       </c>
       <c r="F22">
-        <v>62.56</v>
+        <v>65.688</v>
       </c>
       <c r="G22">
         <v>16.9</v>
@@ -3219,28 +3219,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M22">
-        <v>3.459568</v>
+        <v>3.6325464</v>
       </c>
       <c r="N22">
-        <v>16.96084016326531</v>
+        <v>16.78786176326531</v>
       </c>
       <c r="O22">
-        <v>3.392168032653061</v>
+        <v>3.357572352653062</v>
       </c>
       <c r="P22">
-        <v>13.56867213061225</v>
+        <v>13.43028941061225</v>
       </c>
       <c r="Q22">
-        <v>24.16867213061224</v>
+        <v>24.03028941061224</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09815461730391259</v>
+        <v>0.09870688119952351</v>
       </c>
       <c r="T22">
-        <v>1.0204889388512</v>
+        <v>1.031253590104904</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.902589040962717</v>
+        <v>5.621513372345445</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08726883614762358</v>
+        <v>0.08716597845211706</v>
       </c>
       <c r="C23">
-        <v>255.5223181515253</v>
+        <v>253.1509945125149</v>
       </c>
       <c r="D23">
-        <v>304.3103181515253</v>
+        <v>305.066994512515</v>
       </c>
       <c r="E23">
-        <v>-21.11199999999999</v>
+        <v>-17.98399999999999</v>
       </c>
       <c r="F23">
-        <v>65.688</v>
+        <v>68.816</v>
       </c>
       <c r="G23">
         <v>16.9</v>
@@ -3301,28 +3301,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M23">
-        <v>3.6325464</v>
+        <v>3.8055248</v>
       </c>
       <c r="N23">
-        <v>16.78786176326531</v>
+        <v>16.61488336326531</v>
       </c>
       <c r="O23">
-        <v>3.357572352653062</v>
+        <v>3.322976672653061</v>
       </c>
       <c r="P23">
-        <v>13.43028941061225</v>
+        <v>13.29190669061225</v>
       </c>
       <c r="Q23">
-        <v>24.03028941061224</v>
+        <v>23.89190669061225</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09870688119952351</v>
+        <v>0.09927330570784237</v>
       </c>
       <c r="T23">
-        <v>1.031253590104904</v>
+        <v>1.042294258057422</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.621513372345445</v>
+        <v>5.365990037238834</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08716597845211706</v>
+        <v>0.08706312075661052</v>
       </c>
       <c r="C24">
-        <v>253.1509945125149</v>
+        <v>250.783443248706</v>
       </c>
       <c r="D24">
-        <v>305.066994512515</v>
+        <v>305.8274432487061</v>
       </c>
       <c r="E24">
-        <v>-17.98399999999999</v>
+        <v>-14.85599999999999</v>
       </c>
       <c r="F24">
-        <v>68.816</v>
+        <v>71.944</v>
       </c>
       <c r="G24">
         <v>16.9</v>
@@ -3383,28 +3383,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M24">
-        <v>3.8055248</v>
+        <v>3.9785032</v>
       </c>
       <c r="N24">
-        <v>16.61488336326531</v>
+        <v>16.44190496326531</v>
       </c>
       <c r="O24">
-        <v>3.322976672653061</v>
+        <v>3.288380992653062</v>
       </c>
       <c r="P24">
-        <v>13.29190669061225</v>
+        <v>13.15352397061225</v>
       </c>
       <c r="Q24">
-        <v>23.89190669061225</v>
+        <v>23.75352397061224</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09927330570784237</v>
+        <v>0.09985444254105262</v>
       </c>
       <c r="T24">
-        <v>1.042294258057422</v>
+        <v>1.053621696606109</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.365990037238834</v>
+        <v>5.132686122576276</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08706312075661052</v>
+        <v>0.08696026306110401</v>
       </c>
       <c r="C25">
-        <v>250.783443248706</v>
+        <v>248.4196926410996</v>
       </c>
       <c r="D25">
-        <v>305.8274432487061</v>
+        <v>306.5916926410997</v>
       </c>
       <c r="E25">
-        <v>-14.85599999999999</v>
+        <v>-11.72799999999999</v>
       </c>
       <c r="F25">
-        <v>71.944</v>
+        <v>75.072</v>
       </c>
       <c r="G25">
         <v>16.9</v>
@@ -3465,28 +3465,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M25">
-        <v>3.9785032</v>
+        <v>4.1514816</v>
       </c>
       <c r="N25">
-        <v>16.44190496326531</v>
+        <v>16.26892656326531</v>
       </c>
       <c r="O25">
-        <v>3.288380992653062</v>
+        <v>3.253785312653061</v>
       </c>
       <c r="P25">
-        <v>13.15352397061225</v>
+        <v>13.01514125061225</v>
       </c>
       <c r="Q25">
-        <v>23.75352397061224</v>
+        <v>23.61514125061224</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09985444254105262</v>
+        <v>0.100450872448821</v>
       </c>
       <c r="T25">
-        <v>1.053621696606109</v>
+        <v>1.065247225642919</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.132686122576276</v>
+        <v>4.918824200802264</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08696026306110401</v>
+        <v>0.08685740536559747</v>
       </c>
       <c r="C26">
-        <v>248.4196926410996</v>
+        <v>246.0597712540979</v>
       </c>
       <c r="D26">
-        <v>306.5916926410997</v>
+        <v>307.3597712540979</v>
       </c>
       <c r="E26">
-        <v>-11.72799999999999</v>
+        <v>-8.599999999999994</v>
       </c>
       <c r="F26">
-        <v>75.072</v>
+        <v>78.2</v>
       </c>
       <c r="G26">
         <v>16.9</v>
@@ -3547,28 +3547,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M26">
-        <v>4.1514816</v>
+        <v>4.32446</v>
       </c>
       <c r="N26">
-        <v>16.26892656326531</v>
+        <v>16.09594816326531</v>
       </c>
       <c r="O26">
-        <v>3.253785312653061</v>
+        <v>3.219189632653061</v>
       </c>
       <c r="P26">
-        <v>13.01514125061225</v>
+        <v>12.87675853061224</v>
       </c>
       <c r="Q26">
-        <v>23.61514125061224</v>
+        <v>23.47675853061224</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.100450872448821</v>
+        <v>0.10106320715413</v>
       </c>
       <c r="T26">
-        <v>1.065247225642919</v>
+        <v>1.077182768787377</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.918824200802264</v>
+        <v>4.722071232770173</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08685740536559747</v>
+        <v>0.08675454767009096</v>
       </c>
       <c r="C27">
-        <v>246.0597712540979</v>
+        <v>243.7037079390607</v>
       </c>
       <c r="D27">
-        <v>307.3597712540979</v>
+        <v>308.1317079390607</v>
       </c>
       <c r="E27">
-        <v>-8.599999999999994</v>
+        <v>-5.471999999999994</v>
       </c>
       <c r="F27">
-        <v>78.2</v>
+        <v>81.328</v>
       </c>
       <c r="G27">
         <v>16.9</v>
@@ -3629,28 +3629,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M27">
-        <v>4.32446</v>
+        <v>4.4974384</v>
       </c>
       <c r="N27">
-        <v>16.09594816326531</v>
+        <v>15.92296976326531</v>
       </c>
       <c r="O27">
-        <v>3.219189632653061</v>
+        <v>3.184593952653062</v>
       </c>
       <c r="P27">
-        <v>12.87675853061224</v>
+        <v>12.73837581061225</v>
       </c>
       <c r="Q27">
-        <v>23.47675853061224</v>
+        <v>23.33837581061224</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.10106320715413</v>
+        <v>0.1016920914460689</v>
       </c>
       <c r="T27">
-        <v>1.077182768787377</v>
+        <v>1.089440894178983</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.722071232770173</v>
+        <v>4.54045310843286</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08675454767009096</v>
+        <v>0.08719168997458444</v>
       </c>
       <c r="C28">
-        <v>243.7037079390607</v>
+        <v>237.3214942314614</v>
       </c>
       <c r="D28">
-        <v>308.1317079390607</v>
+        <v>304.8774942314614</v>
       </c>
       <c r="E28">
-        <v>-5.471999999999994</v>
+        <v>-2.343999999999994</v>
       </c>
       <c r="F28">
-        <v>81.328</v>
+        <v>84.456</v>
       </c>
       <c r="G28">
         <v>16.9</v>
@@ -3711,45 +3711,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M28">
-        <v>4.4974384</v>
+        <v>4.8815568</v>
       </c>
       <c r="N28">
-        <v>15.92296976326531</v>
+        <v>15.53885136326531</v>
       </c>
       <c r="O28">
-        <v>3.184593952653062</v>
+        <v>3.107770272653061</v>
       </c>
       <c r="P28">
-        <v>12.73837581061225</v>
+        <v>12.43108109061225</v>
       </c>
       <c r="Q28">
-        <v>23.33837581061224</v>
+        <v>23.03108109061224</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1016920914460689</v>
+        <v>0.1023382054446362</v>
       </c>
       <c r="T28">
-        <v>1.089440894178983</v>
+        <v>1.102034858622414</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.54045310843286</v>
+        <v>4.183175368002541</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08719168997458444</v>
+        <v>0.08710883227907791</v>
       </c>
       <c r="C29">
-        <v>237.3214942314614</v>
+        <v>234.8050207547279</v>
       </c>
       <c r="D29">
-        <v>304.8774942314614</v>
+        <v>305.4890207547279</v>
       </c>
       <c r="E29">
-        <v>-2.343999999999994</v>
+        <v>0.7840000000000202</v>
       </c>
       <c r="F29">
-        <v>84.456</v>
+        <v>87.58400000000002</v>
       </c>
       <c r="G29">
         <v>16.9</v>
@@ -3793,28 +3793,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M29">
-        <v>4.8815568</v>
+        <v>5.062355200000002</v>
       </c>
       <c r="N29">
-        <v>15.53885136326531</v>
+        <v>15.3580529632653</v>
       </c>
       <c r="O29">
-        <v>3.107770272653061</v>
+        <v>3.071610592653061</v>
       </c>
       <c r="P29">
-        <v>12.43108109061225</v>
+        <v>12.28644237061224</v>
       </c>
       <c r="Q29">
-        <v>23.03108109061224</v>
+        <v>22.88644237061224</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1023382054446362</v>
+        <v>0.1030022670542749</v>
       </c>
       <c r="T29">
-        <v>1.102034858622414</v>
+        <v>1.114978655411496</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.183175368002541</v>
+        <v>4.033776247716735</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08710883227907791</v>
+        <v>0.08783797458357138</v>
       </c>
       <c r="C30">
-        <v>234.8050207547279</v>
+        <v>226.3783599415686</v>
       </c>
       <c r="D30">
-        <v>305.4890207547279</v>
+        <v>300.1903599415687</v>
       </c>
       <c r="E30">
-        <v>0.7840000000000202</v>
+        <v>3.91200000000002</v>
       </c>
       <c r="F30">
-        <v>87.58400000000002</v>
+        <v>90.71200000000002</v>
       </c>
       <c r="G30">
         <v>16.9</v>
@@ -3875,45 +3875,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M30">
-        <v>5.062355200000002</v>
+        <v>5.560645600000001</v>
       </c>
       <c r="N30">
-        <v>15.3580529632653</v>
+        <v>14.85976256326531</v>
       </c>
       <c r="O30">
-        <v>3.071610592653061</v>
+        <v>2.971952512653061</v>
       </c>
       <c r="P30">
-        <v>12.28644237061224</v>
+        <v>11.88781005061225</v>
       </c>
       <c r="Q30">
-        <v>22.88644237061224</v>
+        <v>22.48781005061224</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1030022670542749</v>
+        <v>0.1036850346247484</v>
       </c>
       <c r="T30">
-        <v>1.114978655411496</v>
+        <v>1.128287066194636</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.033776247716735</v>
+        <v>3.67230887062202</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08783797458357138</v>
+        <v>0.08778311688806487</v>
       </c>
       <c r="C31">
-        <v>226.3783599415686</v>
+        <v>223.6426069346533</v>
       </c>
       <c r="D31">
-        <v>300.1903599415687</v>
+        <v>300.5826069346533</v>
       </c>
       <c r="E31">
-        <v>3.912000000000006</v>
+        <v>7.040000000000006</v>
       </c>
       <c r="F31">
-        <v>90.712</v>
+        <v>93.84</v>
       </c>
       <c r="G31">
         <v>16.9</v>
@@ -3957,28 +3957,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M31">
-        <v>5.5606456</v>
+        <v>5.752392</v>
       </c>
       <c r="N31">
-        <v>14.85976256326531</v>
+        <v>14.66801616326531</v>
       </c>
       <c r="O31">
-        <v>2.971952512653061</v>
+        <v>2.933603232653061</v>
       </c>
       <c r="P31">
-        <v>11.88781005061225</v>
+        <v>11.73441293061225</v>
       </c>
       <c r="Q31">
-        <v>22.48781005061224</v>
+        <v>22.33441293061225</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1036850346247484</v>
+        <v>0.1043873098400927</v>
       </c>
       <c r="T31">
-        <v>1.128287066194636</v>
+        <v>1.141975717285866</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.67230887062202</v>
+        <v>3.54989857493462</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08778311688806487</v>
+        <v>0.08842265919255834</v>
       </c>
       <c r="C32">
-        <v>223.6426069346533</v>
+        <v>216.0044403525737</v>
       </c>
       <c r="D32">
-        <v>300.5826069346533</v>
+        <v>296.0724403525737</v>
       </c>
       <c r="E32">
-        <v>7.040000000000006</v>
+        <v>10.16800000000001</v>
       </c>
       <c r="F32">
-        <v>93.84</v>
+        <v>96.968</v>
       </c>
       <c r="G32">
         <v>16.9</v>
@@ -4039,45 +4039,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M32">
-        <v>5.752392</v>
+        <v>6.2156488</v>
       </c>
       <c r="N32">
-        <v>14.66801616326531</v>
+        <v>14.20475936326531</v>
       </c>
       <c r="O32">
-        <v>2.933603232653061</v>
+        <v>2.840951872653061</v>
       </c>
       <c r="P32">
-        <v>11.73441293061225</v>
+        <v>11.36380749061225</v>
       </c>
       <c r="Q32">
-        <v>22.33441293061225</v>
+        <v>21.96380749061224</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1043873098400927</v>
+        <v>0.1051099408587802</v>
       </c>
       <c r="T32">
-        <v>1.141975717285866</v>
+        <v>1.156061140872494</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.54989857493462</v>
+        <v>3.285322066984432</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08842265919255834</v>
+        <v>0.08839020149705182</v>
       </c>
       <c r="C33">
-        <v>216.0044403525737</v>
+        <v>213.1020750943464</v>
       </c>
       <c r="D33">
-        <v>296.0724403525737</v>
+        <v>296.2980750943465</v>
       </c>
       <c r="E33">
-        <v>10.16800000000001</v>
+        <v>13.29600000000001</v>
       </c>
       <c r="F33">
-        <v>96.968</v>
+        <v>100.096</v>
       </c>
       <c r="G33">
         <v>16.9</v>
@@ -4121,28 +4121,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M33">
-        <v>6.2156488</v>
+        <v>6.4161536</v>
       </c>
       <c r="N33">
-        <v>14.20475936326531</v>
+        <v>14.00425456326531</v>
       </c>
       <c r="O33">
-        <v>2.840951872653061</v>
+        <v>2.800850912653061</v>
       </c>
       <c r="P33">
-        <v>11.36380749061225</v>
+        <v>11.20340365061224</v>
       </c>
       <c r="Q33">
-        <v>21.96380749061224</v>
+        <v>21.80340365061224</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1051099408587802</v>
+        <v>0.1058538257309586</v>
       </c>
       <c r="T33">
-        <v>1.156061140872494</v>
+        <v>1.170560841623435</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.285322066984432</v>
+        <v>3.182655752391168</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08839020149705182</v>
+        <v>0.0883577438015453</v>
       </c>
       <c r="C34">
-        <v>213.1020750943464</v>
+        <v>210.2000540077358</v>
       </c>
       <c r="D34">
-        <v>296.2980750943465</v>
+        <v>296.5240540077359</v>
       </c>
       <c r="E34">
-        <v>13.29600000000001</v>
+        <v>16.42400000000001</v>
       </c>
       <c r="F34">
-        <v>100.096</v>
+        <v>103.224</v>
       </c>
       <c r="G34">
         <v>16.9</v>
@@ -4203,28 +4203,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M34">
-        <v>6.4161536</v>
+        <v>6.6166584</v>
       </c>
       <c r="N34">
-        <v>14.00425456326531</v>
+        <v>13.80374976326531</v>
       </c>
       <c r="O34">
-        <v>2.800850912653061</v>
+        <v>2.760749952653061</v>
       </c>
       <c r="P34">
-        <v>11.20340365061224</v>
+        <v>11.04299981061225</v>
       </c>
       <c r="Q34">
-        <v>21.80340365061224</v>
+        <v>21.64299981061225</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1058538257309586</v>
+        <v>0.1066199161217094</v>
       </c>
       <c r="T34">
-        <v>1.170560841623435</v>
+        <v>1.185493369262463</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.182655752391168</v>
+        <v>3.086211638682345</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0883577438015453</v>
+        <v>0.09044688610603878</v>
       </c>
       <c r="C35">
-        <v>210.2000540077358</v>
+        <v>193.1969330405945</v>
       </c>
       <c r="D35">
-        <v>296.5240540077359</v>
+        <v>282.6489330405946</v>
       </c>
       <c r="E35">
-        <v>16.42400000000001</v>
+        <v>19.55200000000002</v>
       </c>
       <c r="F35">
-        <v>103.224</v>
+        <v>106.352</v>
       </c>
       <c r="G35">
         <v>16.9</v>
@@ -4285,45 +4285,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M35">
-        <v>6.6166584</v>
+        <v>7.646708800000002</v>
       </c>
       <c r="N35">
-        <v>13.80374976326531</v>
+        <v>12.7736993632653</v>
       </c>
       <c r="O35">
-        <v>2.760749952653061</v>
+        <v>2.554739872653061</v>
       </c>
       <c r="P35">
-        <v>11.04299981061225</v>
+        <v>10.21895949061224</v>
       </c>
       <c r="Q35">
-        <v>21.64299981061225</v>
+        <v>20.81895949061224</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1066199161217094</v>
+        <v>0.107409221372786</v>
       </c>
       <c r="T35">
-        <v>1.185493369262463</v>
+        <v>1.200878397739038</v>
       </c>
       <c r="U35">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>3.086211638682345</v>
+        <v>2.670483301687296</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09044688610603878</v>
+        <v>0.09047682841053226</v>
       </c>
       <c r="C36">
-        <v>193.1969330405945</v>
+        <v>189.8795023956953</v>
       </c>
       <c r="D36">
-        <v>282.6489330405946</v>
+        <v>282.4595023956954</v>
       </c>
       <c r="E36">
-        <v>19.55200000000002</v>
+        <v>22.68000000000002</v>
       </c>
       <c r="F36">
-        <v>106.352</v>
+        <v>109.48</v>
       </c>
       <c r="G36">
         <v>16.9</v>
@@ -4367,28 +4367,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M36">
-        <v>7.646708800000002</v>
+        <v>7.871612000000002</v>
       </c>
       <c r="N36">
-        <v>12.7736993632653</v>
+        <v>12.5487961632653</v>
       </c>
       <c r="O36">
-        <v>2.554739872653061</v>
+        <v>2.509759232653061</v>
       </c>
       <c r="P36">
-        <v>10.21895949061224</v>
+        <v>10.03903693061224</v>
       </c>
       <c r="Q36">
-        <v>20.81895949061224</v>
+        <v>20.63903693061224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.107409221372786</v>
+        <v>0.1082228129392804</v>
       </c>
       <c r="T36">
-        <v>1.200878397739038</v>
+        <v>1.216736811707199</v>
       </c>
       <c r="U36">
         <v>0.07190000000000001</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.670483301687296</v>
+        <v>2.594183778781945</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09047682841053226</v>
+        <v>0.09050677071502575</v>
       </c>
       <c r="C37">
-        <v>189.8795023956953</v>
+        <v>186.5623254926772</v>
       </c>
       <c r="D37">
-        <v>282.4595023956954</v>
+        <v>282.2703254926772</v>
       </c>
       <c r="E37">
-        <v>22.68000000000002</v>
+        <v>25.80800000000002</v>
       </c>
       <c r="F37">
-        <v>109.48</v>
+        <v>112.608</v>
       </c>
       <c r="G37">
         <v>16.9</v>
@@ -4449,28 +4449,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M37">
-        <v>7.871612000000002</v>
+        <v>8.096515200000002</v>
       </c>
       <c r="N37">
-        <v>12.5487961632653</v>
+        <v>12.3238929632653</v>
       </c>
       <c r="O37">
-        <v>2.509759232653061</v>
+        <v>2.464778592653061</v>
       </c>
       <c r="P37">
-        <v>10.03903693061224</v>
+        <v>9.859114370612243</v>
       </c>
       <c r="Q37">
-        <v>20.63903693061224</v>
+        <v>20.45911437061224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1082228129392804</v>
+        <v>0.1090618292422277</v>
       </c>
       <c r="T37">
-        <v>1.216736811707199</v>
+        <v>1.233090801111866</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.594183778781945</v>
+        <v>2.522123118260224</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09050677071502575</v>
+        <v>0.09169111301951924</v>
       </c>
       <c r="C38">
-        <v>186.5623254926772</v>
+        <v>176.1495885188336</v>
       </c>
       <c r="D38">
-        <v>282.2703254926772</v>
+        <v>274.9855885188337</v>
       </c>
       <c r="E38">
-        <v>25.80800000000001</v>
+        <v>28.93600000000001</v>
       </c>
       <c r="F38">
-        <v>112.608</v>
+        <v>115.736</v>
       </c>
       <c r="G38">
         <v>16.9</v>
@@ -4531,45 +4531,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M38">
-        <v>8.096515200000001</v>
+        <v>8.772788800000001</v>
       </c>
       <c r="N38">
-        <v>12.32389296326531</v>
+        <v>11.64761936326531</v>
       </c>
       <c r="O38">
-        <v>2.464778592653062</v>
+        <v>2.329523872653061</v>
       </c>
       <c r="P38">
-        <v>9.859114370612245</v>
+        <v>9.318095490612246</v>
       </c>
       <c r="Q38">
-        <v>20.45911437061224</v>
+        <v>19.91809549061225</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1090618292422277</v>
+        <v>0.1099274809833639</v>
       </c>
       <c r="T38">
-        <v>1.233090801111866</v>
+        <v>1.249963964783348</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.2</v>
       </c>
       <c r="W38">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.522123118260224</v>
+        <v>2.327698594917195</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09169111301951924</v>
+        <v>0.09175225532401271</v>
       </c>
       <c r="C39">
-        <v>176.1495885188336</v>
+        <v>172.6557032654117</v>
       </c>
       <c r="D39">
-        <v>274.9855885188337</v>
+        <v>274.6197032654118</v>
       </c>
       <c r="E39">
-        <v>28.93600000000001</v>
+        <v>32.06400000000001</v>
       </c>
       <c r="F39">
-        <v>115.736</v>
+        <v>118.864</v>
       </c>
       <c r="G39">
         <v>16.9</v>
@@ -4613,28 +4613,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M39">
-        <v>8.772788800000001</v>
+        <v>9.0098912</v>
       </c>
       <c r="N39">
-        <v>11.64761936326531</v>
+        <v>11.41051696326531</v>
       </c>
       <c r="O39">
-        <v>2.329523872653061</v>
+        <v>2.282103392653061</v>
       </c>
       <c r="P39">
-        <v>9.318095490612246</v>
+        <v>9.128413570612246</v>
       </c>
       <c r="Q39">
-        <v>19.91809549061225</v>
+        <v>19.72841357061224</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1099274809833639</v>
+        <v>0.110821056974214</v>
       </c>
       <c r="T39">
-        <v>1.249963964783348</v>
+        <v>1.267381424057135</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.327698594917195</v>
+        <v>2.266443368735164</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09175225532401271</v>
+        <v>0.0918133976285062</v>
       </c>
       <c r="C40">
-        <v>172.6557032654117</v>
+        <v>169.1627903838956</v>
       </c>
       <c r="D40">
-        <v>274.6197032654118</v>
+        <v>274.2547903838956</v>
       </c>
       <c r="E40">
-        <v>32.06400000000001</v>
+        <v>35.19200000000001</v>
       </c>
       <c r="F40">
-        <v>118.864</v>
+        <v>121.992</v>
       </c>
       <c r="G40">
         <v>16.9</v>
@@ -4695,28 +4695,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M40">
-        <v>9.0098912</v>
+        <v>9.246993600000001</v>
       </c>
       <c r="N40">
-        <v>11.41051696326531</v>
+        <v>11.17341456326531</v>
       </c>
       <c r="O40">
-        <v>2.282103392653061</v>
+        <v>2.234682912653061</v>
       </c>
       <c r="P40">
-        <v>9.128413570612246</v>
+        <v>8.938731650612244</v>
       </c>
       <c r="Q40">
-        <v>19.72841357061224</v>
+        <v>19.53873165061224</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.110821056974214</v>
+        <v>0.1117439305385347</v>
       </c>
       <c r="T40">
-        <v>1.267381424057135</v>
+        <v>1.285369947569407</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.266443368735164</v>
+        <v>2.208329436203493</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0918133976285062</v>
+        <v>0.09187453993299965</v>
       </c>
       <c r="C41">
-        <v>169.1627903838956</v>
+        <v>165.670846003185</v>
       </c>
       <c r="D41">
-        <v>274.2547903838956</v>
+        <v>273.890846003185</v>
       </c>
       <c r="E41">
-        <v>35.19200000000001</v>
+        <v>38.32000000000001</v>
       </c>
       <c r="F41">
-        <v>121.992</v>
+        <v>125.12</v>
       </c>
       <c r="G41">
         <v>16.9</v>
@@ -4777,28 +4777,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M41">
-        <v>9.246993600000001</v>
+        <v>9.484096000000001</v>
       </c>
       <c r="N41">
-        <v>11.17341456326531</v>
+        <v>10.93631216326531</v>
       </c>
       <c r="O41">
-        <v>2.234682912653061</v>
+        <v>2.187262432653061</v>
       </c>
       <c r="P41">
-        <v>8.938731650612244</v>
+        <v>8.749049730612246</v>
       </c>
       <c r="Q41">
-        <v>19.53873165061224</v>
+        <v>19.34904973061224</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1117439305385347</v>
+        <v>0.1126975665549994</v>
       </c>
       <c r="T41">
-        <v>1.285369947569407</v>
+        <v>1.303958088532088</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.208329436203493</v>
+        <v>2.153121200298405</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09187453993299965</v>
+        <v>0.09193568223749314</v>
       </c>
       <c r="C42">
-        <v>165.670846003185</v>
+        <v>162.1798662727</v>
       </c>
       <c r="D42">
-        <v>273.890846003185</v>
+        <v>273.5278662727001</v>
       </c>
       <c r="E42">
-        <v>38.32000000000001</v>
+        <v>41.44800000000002</v>
       </c>
       <c r="F42">
-        <v>125.12</v>
+        <v>128.248</v>
       </c>
       <c r="G42">
         <v>16.9</v>
@@ -4859,28 +4859,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M42">
-        <v>9.484096000000001</v>
+        <v>9.721198400000002</v>
       </c>
       <c r="N42">
-        <v>10.93631216326531</v>
+        <v>10.6992097632653</v>
       </c>
       <c r="O42">
-        <v>2.187262432653061</v>
+        <v>2.139841952653061</v>
       </c>
       <c r="P42">
-        <v>8.749049730612246</v>
+        <v>8.559367810612244</v>
       </c>
       <c r="Q42">
-        <v>19.34904973061224</v>
+        <v>19.15936781061224</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1126975665549994</v>
+        <v>0.1136835292160901</v>
       </c>
       <c r="T42">
-        <v>1.303958088532088</v>
+        <v>1.323176335968081</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.153121200298405</v>
+        <v>2.100606049071615</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09193568223749314</v>
+        <v>0.09199682454198663</v>
       </c>
       <c r="C43">
-        <v>162.1798662727</v>
+        <v>158.6898473622466</v>
       </c>
       <c r="D43">
-        <v>273.5278662727001</v>
+        <v>273.1658473622466</v>
       </c>
       <c r="E43">
-        <v>41.44800000000002</v>
+        <v>44.57600000000001</v>
       </c>
       <c r="F43">
-        <v>128.248</v>
+        <v>131.376</v>
       </c>
       <c r="G43">
         <v>16.9</v>
@@ -4941,28 +4941,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M43">
-        <v>9.721198400000002</v>
+        <v>9.958300800000002</v>
       </c>
       <c r="N43">
-        <v>10.6992097632653</v>
+        <v>10.46210736326531</v>
       </c>
       <c r="O43">
-        <v>2.139841952653061</v>
+        <v>2.092421472653061</v>
       </c>
       <c r="P43">
-        <v>8.559367810612244</v>
+        <v>8.369685890612244</v>
       </c>
       <c r="Q43">
-        <v>19.15936781061224</v>
+        <v>18.96968589061224</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1136835292160901</v>
+        <v>0.1147034905896321</v>
       </c>
       <c r="T43">
-        <v>1.323176335968081</v>
+        <v>1.343057281591521</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.100606049071615</v>
+        <v>2.050591619331815</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09199682454198661</v>
+        <v>0.09205796684648011</v>
       </c>
       <c r="C44">
-        <v>158.6898473622466</v>
+        <v>155.2007854618809</v>
       </c>
       <c r="D44">
-        <v>273.1658473622467</v>
+        <v>272.8047854618809</v>
       </c>
       <c r="E44">
-        <v>44.57600000000001</v>
+        <v>47.70399999999999</v>
       </c>
       <c r="F44">
-        <v>131.376</v>
+        <v>134.504</v>
       </c>
       <c r="G44">
         <v>16.9</v>
@@ -5023,28 +5023,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M44">
-        <v>9.958300800000002</v>
+        <v>10.1954032</v>
       </c>
       <c r="N44">
-        <v>10.46210736326531</v>
+        <v>10.22500496326531</v>
       </c>
       <c r="O44">
-        <v>2.092421472653061</v>
+        <v>2.045000992653061</v>
       </c>
       <c r="P44">
-        <v>8.369685890612244</v>
+        <v>8.180003970612246</v>
       </c>
       <c r="Q44">
-        <v>18.96968589061224</v>
+        <v>18.78000397061224</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1147034905896321</v>
+        <v>0.115759240081544</v>
       </c>
       <c r="T44">
-        <v>1.343057281591521</v>
+        <v>1.363635804254381</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.050591619331815</v>
+        <v>2.002903442138052</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09205796684648011</v>
+        <v>0.09711750915097359</v>
       </c>
       <c r="C45">
-        <v>155.2007854618809</v>
+        <v>125.1761691656383</v>
       </c>
       <c r="D45">
-        <v>272.8047854618809</v>
+        <v>245.9081691656384</v>
       </c>
       <c r="E45">
-        <v>47.70399999999999</v>
+        <v>50.83200000000001</v>
       </c>
       <c r="F45">
-        <v>134.504</v>
+        <v>137.632</v>
       </c>
       <c r="G45">
         <v>16.9</v>
@@ -5105,45 +5105,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M45">
-        <v>10.1954032</v>
+        <v>12.38688</v>
       </c>
       <c r="N45">
-        <v>10.22500496326531</v>
+        <v>8.033528163265307</v>
       </c>
       <c r="O45">
-        <v>2.045000992653061</v>
+        <v>1.606705632653062</v>
       </c>
       <c r="P45">
-        <v>8.180003970612246</v>
+        <v>6.426822530612246</v>
       </c>
       <c r="Q45">
-        <v>18.78000397061224</v>
+        <v>17.02682253061224</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.115759240081544</v>
+        <v>0.1168526949124528</v>
       </c>
       <c r="T45">
-        <v>1.363635804254381</v>
+        <v>1.384949274155199</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.002903442138052</v>
+        <v>1.64855138366282</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09711750915097359</v>
+        <v>0.09729225145546705</v>
       </c>
       <c r="C46">
-        <v>125.1761691656383</v>
+        <v>121.2136637991186</v>
       </c>
       <c r="D46">
-        <v>245.9081691656384</v>
+        <v>245.0736637991186</v>
       </c>
       <c r="E46">
-        <v>50.83200000000001</v>
+        <v>53.96000000000002</v>
       </c>
       <c r="F46">
-        <v>137.632</v>
+        <v>140.76</v>
       </c>
       <c r="G46">
         <v>16.9</v>
@@ -5187,28 +5187,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M46">
-        <v>12.38688</v>
+        <v>12.6684</v>
       </c>
       <c r="N46">
-        <v>8.033528163265307</v>
+        <v>7.752008163265305</v>
       </c>
       <c r="O46">
-        <v>1.606705632653062</v>
+        <v>1.550401632653061</v>
       </c>
       <c r="P46">
-        <v>6.426822530612246</v>
+        <v>6.201606530612244</v>
       </c>
       <c r="Q46">
-        <v>17.02682253061224</v>
+        <v>16.80160653061224</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1168526949124528</v>
+        <v>0.1179859117372128</v>
       </c>
       <c r="T46">
-        <v>1.384949274155199</v>
+        <v>1.407037779325139</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.64855138366282</v>
+        <v>1.611916908470312</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09729225145546705</v>
+        <v>0.09746699375996054</v>
       </c>
       <c r="C47">
-        <v>121.2136637991186</v>
+        <v>117.2568031732831</v>
       </c>
       <c r="D47">
-        <v>245.0736637991186</v>
+        <v>244.2448031732831</v>
       </c>
       <c r="E47">
-        <v>53.96000000000002</v>
+        <v>57.08800000000001</v>
       </c>
       <c r="F47">
-        <v>140.76</v>
+        <v>143.888</v>
       </c>
       <c r="G47">
         <v>16.9</v>
@@ -5269,28 +5269,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M47">
-        <v>12.6684</v>
+        <v>12.94992</v>
       </c>
       <c r="N47">
-        <v>7.752008163265305</v>
+        <v>7.470488163265307</v>
       </c>
       <c r="O47">
-        <v>1.550401632653061</v>
+        <v>1.494097632653062</v>
       </c>
       <c r="P47">
-        <v>6.201606530612244</v>
+        <v>5.976390530612245</v>
       </c>
       <c r="Q47">
-        <v>16.80160653061224</v>
+        <v>16.57639053061224</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1179859117372128</v>
+        <v>0.1191610995554825</v>
       </c>
       <c r="T47">
-        <v>1.407037779325139</v>
+        <v>1.42994437727915</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.611916908470312</v>
+        <v>1.576875236547045</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09746699375996054</v>
+        <v>0.09764173606445403</v>
       </c>
       <c r="C48">
-        <v>117.2568031732831</v>
+        <v>113.3055302081572</v>
       </c>
       <c r="D48">
-        <v>244.2448031732831</v>
+        <v>243.4215302081572</v>
       </c>
       <c r="E48">
-        <v>57.08800000000001</v>
+        <v>60.21600000000002</v>
       </c>
       <c r="F48">
-        <v>143.888</v>
+        <v>147.016</v>
       </c>
       <c r="G48">
         <v>16.9</v>
@@ -5351,28 +5351,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M48">
-        <v>12.94992</v>
+        <v>13.23144</v>
       </c>
       <c r="N48">
-        <v>7.470488163265307</v>
+        <v>7.188968163265306</v>
       </c>
       <c r="O48">
-        <v>1.494097632653062</v>
+        <v>1.437793632653061</v>
       </c>
       <c r="P48">
-        <v>5.976390530612245</v>
+        <v>5.751174530612245</v>
       </c>
       <c r="Q48">
-        <v>16.57639053061224</v>
+        <v>16.35117453061224</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1191610995554825</v>
+        <v>0.1203806340838755</v>
       </c>
       <c r="T48">
-        <v>1.42994437727915</v>
+        <v>1.453715375155954</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.576875236547045</v>
+        <v>1.543324699599235</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09764173606445403</v>
+        <v>0.0978164783689475</v>
       </c>
       <c r="C49">
-        <v>113.3055302081572</v>
+        <v>109.3597885907759</v>
       </c>
       <c r="D49">
-        <v>243.4215302081572</v>
+        <v>242.6037885907759</v>
       </c>
       <c r="E49">
-        <v>60.21600000000002</v>
+        <v>63.34400000000001</v>
       </c>
       <c r="F49">
-        <v>147.016</v>
+        <v>150.144</v>
       </c>
       <c r="G49">
         <v>16.9</v>
@@ -5433,28 +5433,28 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M49">
-        <v>13.23144</v>
+        <v>13.51296</v>
       </c>
       <c r="N49">
-        <v>7.188968163265306</v>
+        <v>6.907448163265308</v>
       </c>
       <c r="O49">
-        <v>1.437793632653061</v>
+        <v>1.381489632653062</v>
       </c>
       <c r="P49">
-        <v>5.751174530612245</v>
+        <v>5.525958530612246</v>
       </c>
       <c r="Q49">
-        <v>16.35117453061224</v>
+        <v>16.12595853061224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1203806340838755</v>
+        <v>0.1216470737864375</v>
       </c>
       <c r="T49">
-        <v>1.453715375155954</v>
+        <v>1.478400642181866</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.543324699599235</v>
+        <v>1.511172101690918</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0978164783689475</v>
+        <v>0.1219819309658804</v>
       </c>
       <c r="C50">
-        <v>109.3597885907759</v>
+        <v>29.27613416331823</v>
       </c>
       <c r="D50">
-        <v>242.6037885907759</v>
+        <v>165.6481341633182</v>
       </c>
       <c r="E50">
-        <v>63.34400000000001</v>
+        <v>66.47199999999999</v>
       </c>
       <c r="F50">
-        <v>150.144</v>
+        <v>153.272</v>
       </c>
       <c r="G50">
         <v>16.9</v>
@@ -5515,45 +5515,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M50">
-        <v>13.51296</v>
+        <v>22.5003296</v>
       </c>
       <c r="N50">
-        <v>6.907448163265308</v>
+        <v>-2.079921436734693</v>
       </c>
       <c r="O50">
-        <v>1.381489632653062</v>
+        <v>-0.4159842873469387</v>
       </c>
       <c r="P50">
-        <v>5.525958530612246</v>
+        <v>-1.663937149387755</v>
       </c>
       <c r="Q50">
-        <v>16.12595853061224</v>
+        <v>8.936062850612243</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1216470737864375</v>
+        <v>0.1237381527931176</v>
       </c>
       <c r="T50">
-        <v>1.478400642181866</v>
+        <v>1.519159664145369</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.2</v>
+        <v>0.181512080278729</v>
       </c>
       <c r="W50">
-        <v>0.07199999999999999</v>
+        <v>0.1201540266150826</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.511172101690918</v>
+        <v>0.9075604013936448</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1219819309658804</v>
+        <v>0.1229919309658804</v>
       </c>
       <c r="C51">
-        <v>29.27613416331823</v>
+        <v>23.9807493938026</v>
       </c>
       <c r="D51">
-        <v>165.6481341633182</v>
+        <v>163.4807493938026</v>
       </c>
       <c r="E51">
-        <v>66.47199999999999</v>
+        <v>69.60000000000001</v>
       </c>
       <c r="F51">
-        <v>153.272</v>
+        <v>156.4</v>
       </c>
       <c r="G51">
         <v>16.9</v>
@@ -5597,37 +5597,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M51">
-        <v>22.5003296</v>
+        <v>22.95952</v>
       </c>
       <c r="N51">
-        <v>-2.079921436734693</v>
+        <v>-2.539111836734694</v>
       </c>
       <c r="O51">
-        <v>-0.4159842873469387</v>
+        <v>-0.5078223673469389</v>
       </c>
       <c r="P51">
-        <v>-1.663937149387755</v>
+        <v>-2.031289469387755</v>
       </c>
       <c r="Q51">
-        <v>8.936062850612243</v>
+        <v>8.568710530612243</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1237381527931176</v>
+        <v>0.1252969158489799</v>
       </c>
       <c r="T51">
-        <v>1.519159664145369</v>
+        <v>1.549542857428276</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.181512080278729</v>
+        <v>0.1778818386731544</v>
       </c>
       <c r="W51">
-        <v>0.1201540266150826</v>
+        <v>0.1206869460827809</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9075604013936448</v>
+        <v>0.8894091933657718</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1229919309658804</v>
+        <v>0.1240019309658804</v>
       </c>
       <c r="C52">
-        <v>23.9807493938026</v>
+        <v>18.74134939576697</v>
       </c>
       <c r="D52">
-        <v>163.4807493938026</v>
+        <v>161.369349395767</v>
       </c>
       <c r="E52">
-        <v>69.60000000000001</v>
+        <v>72.72800000000002</v>
       </c>
       <c r="F52">
-        <v>156.4</v>
+        <v>159.528</v>
       </c>
       <c r="G52">
         <v>16.9</v>
@@ -5679,37 +5679,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M52">
-        <v>22.95952</v>
+        <v>23.41871040000001</v>
       </c>
       <c r="N52">
-        <v>-2.539111836734694</v>
+        <v>-2.998302236734698</v>
       </c>
       <c r="O52">
-        <v>-0.5078223673469389</v>
+        <v>-0.5996604473469397</v>
       </c>
       <c r="P52">
-        <v>-2.031289469387755</v>
+        <v>-2.398641789387759</v>
       </c>
       <c r="Q52">
-        <v>8.568710530612243</v>
+        <v>8.20135821061224</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1252969158489799</v>
+        <v>0.1269193018867142</v>
       </c>
       <c r="T52">
-        <v>1.549542857428276</v>
+        <v>1.581166181049261</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.1778818386731544</v>
+        <v>0.1743939594834847</v>
       </c>
       <c r="W52">
-        <v>0.1206869460827809</v>
+        <v>0.1211989667478245</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8894091933657718</v>
+        <v>0.8719697974174232</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1240019309658804</v>
+        <v>0.1250119309658804</v>
       </c>
       <c r="C53">
-        <v>18.74134939576697</v>
+        <v>13.55579265018116</v>
       </c>
       <c r="D53">
-        <v>161.369349395767</v>
+        <v>159.3117926501812</v>
       </c>
       <c r="E53">
-        <v>72.72800000000002</v>
+        <v>75.85600000000001</v>
       </c>
       <c r="F53">
-        <v>159.528</v>
+        <v>162.656</v>
       </c>
       <c r="G53">
         <v>16.9</v>
@@ -5761,37 +5761,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M53">
-        <v>23.41871040000001</v>
+        <v>23.8779008</v>
       </c>
       <c r="N53">
-        <v>-2.998302236734698</v>
+        <v>-3.457492636734695</v>
       </c>
       <c r="O53">
-        <v>-0.5996604473469397</v>
+        <v>-0.6914985273469392</v>
       </c>
       <c r="P53">
-        <v>-2.398641789387759</v>
+        <v>-2.765994109387756</v>
       </c>
       <c r="Q53">
-        <v>8.20135821061224</v>
+        <v>7.834005890612241</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1269193018867142</v>
+        <v>0.1286092873426874</v>
       </c>
       <c r="T53">
-        <v>1.581166181049261</v>
+        <v>1.614107143154454</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1743939594834847</v>
+        <v>0.1710402294934177</v>
       </c>
       <c r="W53">
-        <v>0.1211989667478245</v>
+        <v>0.1216912943103663</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8719697974174232</v>
+        <v>0.8552011474670883</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1250119309658804</v>
+        <v>0.1260219309658804</v>
       </c>
       <c r="C54">
-        <v>13.55579265018116</v>
+        <v>8.4220454855421</v>
       </c>
       <c r="D54">
-        <v>159.3117926501812</v>
+        <v>157.3060454855421</v>
       </c>
       <c r="E54">
-        <v>75.85600000000001</v>
+        <v>78.98400000000002</v>
       </c>
       <c r="F54">
-        <v>162.656</v>
+        <v>165.784</v>
       </c>
       <c r="G54">
         <v>16.9</v>
@@ -5843,37 +5843,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M54">
-        <v>23.8779008</v>
+        <v>24.33709120000001</v>
       </c>
       <c r="N54">
-        <v>-3.457492636734695</v>
+        <v>-3.9166830367347</v>
       </c>
       <c r="O54">
-        <v>-0.6914985273469392</v>
+        <v>-0.78333660734694</v>
       </c>
       <c r="P54">
-        <v>-2.765994109387756</v>
+        <v>-3.13334642938776</v>
       </c>
       <c r="Q54">
-        <v>7.834005890612241</v>
+        <v>7.466653570612238</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1286092873426874</v>
+        <v>0.1303711870733829</v>
       </c>
       <c r="T54">
-        <v>1.614107143154454</v>
+        <v>1.648449848327954</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1710402294934177</v>
+        <v>0.1678130553520324</v>
       </c>
       <c r="W54">
-        <v>0.1216912943103663</v>
+        <v>0.1221650434743217</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8552011474670883</v>
+        <v>0.839065276760162</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1260219309658804</v>
+        <v>0.1270319309658804</v>
       </c>
       <c r="C55">
-        <v>8.4220454855421</v>
+        <v>3.338175373244411</v>
       </c>
       <c r="D55">
-        <v>157.3060454855421</v>
+        <v>155.3501753732444</v>
       </c>
       <c r="E55">
-        <v>78.98400000000002</v>
+        <v>82.11200000000001</v>
       </c>
       <c r="F55">
-        <v>165.784</v>
+        <v>168.912</v>
       </c>
       <c r="G55">
         <v>16.9</v>
@@ -5925,37 +5925,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M55">
-        <v>24.33709120000001</v>
+        <v>24.7962816</v>
       </c>
       <c r="N55">
-        <v>-3.9166830367347</v>
+        <v>-4.375873436734697</v>
       </c>
       <c r="O55">
-        <v>-0.78333660734694</v>
+        <v>-0.8751746873469394</v>
       </c>
       <c r="P55">
-        <v>-3.13334642938776</v>
+        <v>-3.500698749387757</v>
       </c>
       <c r="Q55">
-        <v>7.466653570612238</v>
+        <v>7.099301250612241</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1303711870733829</v>
+        <v>0.1322096911401955</v>
       </c>
       <c r="T55">
-        <v>1.648449848327954</v>
+        <v>1.684285714595952</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1678130553520324</v>
+        <v>0.1647054061788466</v>
       </c>
       <c r="W55">
-        <v>0.1221650434743217</v>
+        <v>0.1226212463729453</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.839065276760162</v>
+        <v>0.8235270308942331</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1270319309658804</v>
+        <v>0.1280419309658804</v>
       </c>
       <c r="C56">
-        <v>3.338175373244411</v>
+        <v>-1.697655283018662</v>
       </c>
       <c r="D56">
-        <v>155.3501753732444</v>
+        <v>153.4423447169814</v>
       </c>
       <c r="E56">
-        <v>82.11200000000001</v>
+        <v>85.24000000000002</v>
       </c>
       <c r="F56">
-        <v>168.912</v>
+        <v>172.04</v>
       </c>
       <c r="G56">
         <v>16.9</v>
@@ -6007,37 +6007,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M56">
-        <v>24.7962816</v>
+        <v>25.255472</v>
       </c>
       <c r="N56">
-        <v>-4.375873436734697</v>
+        <v>-4.835063836734697</v>
       </c>
       <c r="O56">
-        <v>-0.8751746873469394</v>
+        <v>-0.9670127673469395</v>
       </c>
       <c r="P56">
-        <v>-3.500698749387757</v>
+        <v>-3.868051069387758</v>
       </c>
       <c r="Q56">
-        <v>7.099301250612241</v>
+        <v>6.73194893061224</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1322096911401955</v>
+        <v>0.1341299064988666</v>
       </c>
       <c r="T56">
-        <v>1.684285714595952</v>
+        <v>1.721714286031418</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1647054061788466</v>
+        <v>0.1617107624301403</v>
       </c>
       <c r="W56">
-        <v>0.1226212463729453</v>
+        <v>0.1230608600752554</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8235270308942331</v>
+        <v>0.8085538121507015</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1280419309658804</v>
+        <v>0.1603354620951314</v>
       </c>
       <c r="C57">
-        <v>-1.697655283018662</v>
+        <v>-48.08906946951225</v>
       </c>
       <c r="D57">
-        <v>153.4423447169814</v>
+        <v>110.1789305304878</v>
       </c>
       <c r="E57">
-        <v>85.24000000000002</v>
+        <v>88.36800000000004</v>
       </c>
       <c r="F57">
-        <v>172.04</v>
+        <v>175.168</v>
       </c>
       <c r="G57">
         <v>16.9</v>
@@ -6089,45 +6089,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M57">
-        <v>25.255472</v>
+        <v>35.17373440000001</v>
       </c>
       <c r="N57">
-        <v>-4.835063836734697</v>
+        <v>-14.7533262367347</v>
       </c>
       <c r="O57">
-        <v>-0.9670127673469395</v>
+        <v>-2.95066524734694</v>
       </c>
       <c r="P57">
-        <v>-3.868051069387758</v>
+        <v>-11.80266098938776</v>
       </c>
       <c r="Q57">
-        <v>6.73194893061224</v>
+        <v>-1.202660989387763</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1341299064988666</v>
+        <v>0.1385090660312295</v>
       </c>
       <c r="T57">
-        <v>1.721714286031418</v>
+        <v>1.807072256242524</v>
       </c>
       <c r="U57">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1617107624301403</v>
+        <v>0.1161116868117666</v>
       </c>
       <c r="W57">
-        <v>0.1230608600752554</v>
+        <v>0.1774847732881973</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.8085538121507015</v>
+        <v>0.5805584340588329</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1603354620951314</v>
+        <v>0.1618854620951315</v>
       </c>
       <c r="C58">
-        <v>-48.08906946951225</v>
+        <v>-52.688204090851</v>
       </c>
       <c r="D58">
-        <v>110.1789305304878</v>
+        <v>108.707795909149</v>
       </c>
       <c r="E58">
-        <v>88.36800000000004</v>
+        <v>91.49600000000002</v>
       </c>
       <c r="F58">
-        <v>175.168</v>
+        <v>178.296</v>
       </c>
       <c r="G58">
         <v>16.9</v>
@@ -6171,37 +6171,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M58">
-        <v>35.17373440000001</v>
+        <v>35.8018368</v>
       </c>
       <c r="N58">
-        <v>-14.7533262367347</v>
+        <v>-15.3814286367347</v>
       </c>
       <c r="O58">
-        <v>-2.95066524734694</v>
+        <v>-3.07628572734694</v>
       </c>
       <c r="P58">
-        <v>-11.80266098938776</v>
+        <v>-12.30514290938776</v>
       </c>
       <c r="Q58">
-        <v>-1.202660989387763</v>
+        <v>-1.70514290938776</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1385090660312295</v>
+        <v>0.1406650908226535</v>
       </c>
       <c r="T58">
-        <v>1.807072256242524</v>
+        <v>1.849097192434211</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1161116868117666</v>
+        <v>0.1140746396747181</v>
       </c>
       <c r="W58">
-        <v>0.1774847732881973</v>
+        <v>0.1778938123533166</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5805584340588329</v>
+        <v>0.5703731983735902</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1618854620951315</v>
+        <v>0.1634354620951315</v>
       </c>
       <c r="C59">
-        <v>-52.688204090851</v>
+        <v>-57.24857049344922</v>
       </c>
       <c r="D59">
-        <v>108.707795909149</v>
+        <v>107.2754295065508</v>
       </c>
       <c r="E59">
-        <v>91.49600000000002</v>
+        <v>94.62400000000004</v>
       </c>
       <c r="F59">
-        <v>178.296</v>
+        <v>181.424</v>
       </c>
       <c r="G59">
         <v>16.9</v>
@@ -6253,37 +6253,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M59">
-        <v>35.8018368</v>
+        <v>36.42993920000001</v>
       </c>
       <c r="N59">
-        <v>-15.3814286367347</v>
+        <v>-16.0095310367347</v>
       </c>
       <c r="O59">
-        <v>-3.07628572734694</v>
+        <v>-3.20190620734694</v>
       </c>
       <c r="P59">
-        <v>-12.30514290938776</v>
+        <v>-12.80762482938776</v>
       </c>
       <c r="Q59">
-        <v>-1.70514290938776</v>
+        <v>-2.207624829387761</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1406650908226535</v>
+        <v>0.1429237834612881</v>
       </c>
       <c r="T59">
-        <v>1.849097192434211</v>
+        <v>1.893123316063596</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1140746396747181</v>
+        <v>0.1121078355423953</v>
       </c>
       <c r="W59">
-        <v>0.1778938123533166</v>
+        <v>0.178288746623087</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5703731983735902</v>
+        <v>0.5605391777119766</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1634354620951315</v>
+        <v>0.1649854620951315</v>
       </c>
       <c r="C60">
-        <v>-57.24857049344919</v>
+        <v>-61.7716812125941</v>
       </c>
       <c r="D60">
-        <v>107.2754295065508</v>
+        <v>105.8803187874059</v>
       </c>
       <c r="E60">
-        <v>94.62400000000001</v>
+        <v>97.752</v>
       </c>
       <c r="F60">
-        <v>181.424</v>
+        <v>184.552</v>
       </c>
       <c r="G60">
         <v>16.9</v>
@@ -6335,37 +6335,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M60">
-        <v>36.4299392</v>
+        <v>37.0580416</v>
       </c>
       <c r="N60">
-        <v>-16.00953103673469</v>
+        <v>-16.6376334367347</v>
       </c>
       <c r="O60">
-        <v>-3.201906207346939</v>
+        <v>-3.327526687346939</v>
       </c>
       <c r="P60">
-        <v>-12.80762482938775</v>
+        <v>-13.31010674938776</v>
       </c>
       <c r="Q60">
-        <v>-2.207624829387756</v>
+        <v>-2.710106749387759</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1429237834612881</v>
+        <v>0.1452926562286366</v>
       </c>
       <c r="T60">
-        <v>1.893123316063596</v>
+        <v>1.939297055479782</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1121078355423953</v>
+        <v>0.110207702736592</v>
       </c>
       <c r="W60">
-        <v>0.178288746623087</v>
+        <v>0.1786702932904923</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5605391777119768</v>
+        <v>0.5510385136829601</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1649854620951315</v>
+        <v>0.1665354620951315</v>
       </c>
       <c r="C61">
-        <v>-61.7716812125941</v>
+        <v>-66.25897111195414</v>
       </c>
       <c r="D61">
-        <v>105.8803187874059</v>
+        <v>104.5210288880459</v>
       </c>
       <c r="E61">
-        <v>97.752</v>
+        <v>100.88</v>
       </c>
       <c r="F61">
-        <v>184.552</v>
+        <v>187.68</v>
       </c>
       <c r="G61">
         <v>16.9</v>
@@ -6417,37 +6417,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M61">
-        <v>37.0580416</v>
+        <v>37.68614400000001</v>
       </c>
       <c r="N61">
-        <v>-16.6376334367347</v>
+        <v>-17.2657358367347</v>
       </c>
       <c r="O61">
-        <v>-3.327526687346939</v>
+        <v>-3.45314716734694</v>
       </c>
       <c r="P61">
-        <v>-13.31010674938776</v>
+        <v>-13.81258866938776</v>
       </c>
       <c r="Q61">
-        <v>-2.710106749387759</v>
+        <v>-3.212588669387761</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1452926562286366</v>
+        <v>0.1477799726343525</v>
       </c>
       <c r="T61">
-        <v>1.939297055479782</v>
+        <v>1.987779481866776</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.110207702736592</v>
+        <v>0.1083709076909821</v>
       </c>
       <c r="W61">
-        <v>0.1786702932904923</v>
+        <v>0.1790391217356508</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5510385136829601</v>
+        <v>0.5418545384549107</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1665354620951315</v>
+        <v>0.1680854620951315</v>
       </c>
       <c r="C62">
-        <v>-66.25897111195414</v>
+        <v>-70.71180230611878</v>
       </c>
       <c r="D62">
-        <v>104.5210288880459</v>
+        <v>103.1961976938812</v>
       </c>
       <c r="E62">
-        <v>100.88</v>
+        <v>104.008</v>
       </c>
       <c r="F62">
-        <v>187.68</v>
+        <v>190.808</v>
       </c>
       <c r="G62">
         <v>16.9</v>
@@ -6499,37 +6499,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M62">
-        <v>37.68614400000001</v>
+        <v>38.3142464</v>
       </c>
       <c r="N62">
-        <v>-17.2657358367347</v>
+        <v>-17.89383823673469</v>
       </c>
       <c r="O62">
-        <v>-3.45314716734694</v>
+        <v>-3.578767647346939</v>
       </c>
       <c r="P62">
-        <v>-13.81258866938776</v>
+        <v>-14.31507058938776</v>
       </c>
       <c r="Q62">
-        <v>-3.212588669387761</v>
+        <v>-3.715070589387757</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1477799726343525</v>
+        <v>0.150394843727541</v>
       </c>
       <c r="T62">
-        <v>1.987779481866776</v>
+        <v>2.038748186530027</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1083709076909821</v>
+        <v>0.1065943354337529</v>
       </c>
       <c r="W62">
-        <v>0.1790391217356508</v>
+        <v>0.1793958574449024</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5418545384549107</v>
+        <v>0.5329716771687647</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1680854620951315</v>
+        <v>0.1696354620951315</v>
       </c>
       <c r="C63">
-        <v>-70.71180230611878</v>
+        <v>-75.13146871345725</v>
       </c>
       <c r="D63">
-        <v>103.1961976938812</v>
+        <v>101.9045312865428</v>
       </c>
       <c r="E63">
-        <v>104.008</v>
+        <v>107.136</v>
       </c>
       <c r="F63">
-        <v>190.808</v>
+        <v>193.936</v>
       </c>
       <c r="G63">
         <v>16.9</v>
@@ -6581,37 +6581,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M63">
-        <v>38.3142464</v>
+        <v>38.9423488</v>
       </c>
       <c r="N63">
-        <v>-17.89383823673469</v>
+        <v>-18.5219406367347</v>
       </c>
       <c r="O63">
-        <v>-3.578767647346939</v>
+        <v>-3.70438812734694</v>
       </c>
       <c r="P63">
-        <v>-14.31507058938776</v>
+        <v>-14.81755250938776</v>
       </c>
       <c r="Q63">
-        <v>-3.715070589387757</v>
+        <v>-4.21755250938776</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.150394843727541</v>
+        <v>0.1531473396151079</v>
       </c>
       <c r="T63">
-        <v>2.038748186530027</v>
+        <v>2.092399454596606</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1065943354337529</v>
+        <v>0.104875071959015</v>
       </c>
       <c r="W63">
-        <v>0.1793958574449024</v>
+        <v>0.1797410855506298</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5329716771687647</v>
+        <v>0.5243753597950749</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1696354620951315</v>
+        <v>0.1711854620951315</v>
       </c>
       <c r="C64">
-        <v>-75.13146871345725</v>
+        <v>-79.51920027128571</v>
       </c>
       <c r="D64">
-        <v>101.9045312865428</v>
+        <v>100.6447997287143</v>
       </c>
       <c r="E64">
-        <v>107.136</v>
+        <v>110.264</v>
       </c>
       <c r="F64">
-        <v>193.936</v>
+        <v>197.064</v>
       </c>
       <c r="G64">
         <v>16.9</v>
@@ -6663,37 +6663,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M64">
-        <v>38.9423488</v>
+        <v>39.57045120000001</v>
       </c>
       <c r="N64">
-        <v>-18.5219406367347</v>
+        <v>-19.1500430367347</v>
       </c>
       <c r="O64">
-        <v>-3.70438812734694</v>
+        <v>-3.83000860734694</v>
       </c>
       <c r="P64">
-        <v>-14.81755250938776</v>
+        <v>-15.32003442938776</v>
       </c>
       <c r="Q64">
-        <v>-4.21755250938776</v>
+        <v>-4.720034429387763</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1531473396151079</v>
+        <v>0.1560486190641649</v>
       </c>
       <c r="T64">
-        <v>2.092399454596606</v>
+        <v>2.148950791207326</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.104875071959015</v>
+        <v>0.1032103882771259</v>
       </c>
       <c r="W64">
-        <v>0.1797410855506298</v>
+        <v>0.1800753540339531</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5243753597950749</v>
+        <v>0.5160519413856293</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1711854620951315</v>
+        <v>0.1727354620951315</v>
       </c>
       <c r="C65">
-        <v>-79.51920027128571</v>
+        <v>-83.87616684220814</v>
       </c>
       <c r="D65">
-        <v>100.6447997287143</v>
+        <v>99.41583315779188</v>
       </c>
       <c r="E65">
-        <v>110.264</v>
+        <v>113.392</v>
       </c>
       <c r="F65">
-        <v>197.064</v>
+        <v>200.192</v>
       </c>
       <c r="G65">
         <v>16.9</v>
@@ -6745,37 +6745,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M65">
-        <v>39.57045120000001</v>
+        <v>40.1985536</v>
       </c>
       <c r="N65">
-        <v>-19.1500430367347</v>
+        <v>-19.7781454367347</v>
       </c>
       <c r="O65">
-        <v>-3.83000860734694</v>
+        <v>-3.95562908734694</v>
       </c>
       <c r="P65">
-        <v>-15.32003442938776</v>
+        <v>-15.82251634938776</v>
       </c>
       <c r="Q65">
-        <v>-4.720034429387763</v>
+        <v>-5.22251634938776</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1560486190641649</v>
+        <v>0.1591110807048361</v>
       </c>
       <c r="T65">
-        <v>2.148950791207326</v>
+        <v>2.208643868740863</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1032103882771259</v>
+        <v>0.1015977259602958</v>
       </c>
       <c r="W65">
-        <v>0.1800753540339531</v>
+        <v>0.1803991766271726</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5160519413856293</v>
+        <v>0.5079886298014789</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1727354620951315</v>
+        <v>0.1742854620951315</v>
       </c>
       <c r="C66">
-        <v>-83.87616684220814</v>
+        <v>-88.20348183770921</v>
       </c>
       <c r="D66">
-        <v>99.41583315779188</v>
+        <v>98.21651816229081</v>
       </c>
       <c r="E66">
-        <v>113.392</v>
+        <v>116.52</v>
       </c>
       <c r="F66">
-        <v>200.192</v>
+        <v>203.32</v>
       </c>
       <c r="G66">
         <v>16.9</v>
@@ -6827,37 +6827,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M66">
-        <v>40.1985536</v>
+        <v>40.82665600000001</v>
       </c>
       <c r="N66">
-        <v>-19.7781454367347</v>
+        <v>-20.4062478367347</v>
       </c>
       <c r="O66">
-        <v>-3.95562908734694</v>
+        <v>-4.08124956734694</v>
       </c>
       <c r="P66">
-        <v>-15.82251634938776</v>
+        <v>-16.32499826938776</v>
       </c>
       <c r="Q66">
-        <v>-5.22251634938776</v>
+        <v>-5.724998269387761</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1591110807048361</v>
+        <v>0.1623485401535457</v>
       </c>
       <c r="T66">
-        <v>2.208643868740863</v>
+        <v>2.271747979276316</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1015977259602958</v>
+        <v>0.1000346840224451</v>
       </c>
       <c r="W66">
-        <v>0.1803991766271726</v>
+        <v>0.180713035448293</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5079886298014789</v>
+        <v>0.5001734201122253</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1742854620951315</v>
+        <v>0.1993565395102425</v>
       </c>
       <c r="C67">
-        <v>-88.20348183770921</v>
+        <v>-107.3672295703885</v>
       </c>
       <c r="D67">
-        <v>98.21651816229081</v>
+        <v>82.1807704296115</v>
       </c>
       <c r="E67">
-        <v>116.52</v>
+        <v>119.648</v>
       </c>
       <c r="F67">
-        <v>203.32</v>
+        <v>206.448</v>
       </c>
       <c r="G67">
         <v>16.9</v>
@@ -6909,45 +6909,45 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M67">
-        <v>40.82665600000001</v>
+        <v>48.68043840000001</v>
       </c>
       <c r="N67">
-        <v>-20.4062478367347</v>
+        <v>-28.2600302367347</v>
       </c>
       <c r="O67">
-        <v>-4.08124956734694</v>
+        <v>-5.652006047346941</v>
       </c>
       <c r="P67">
-        <v>-16.32499826938776</v>
+        <v>-22.60802418938776</v>
       </c>
       <c r="Q67">
-        <v>-5.724998269387761</v>
+        <v>-12.00802418938776</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1623485401535457</v>
+        <v>0.1670149013789766</v>
       </c>
       <c r="T67">
-        <v>2.271747979276316</v>
+        <v>2.362704045053545</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1000346840224451</v>
+        <v>0.08389574471566512</v>
       </c>
       <c r="W67">
-        <v>0.180713035448293</v>
+        <v>0.2160173833960462</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5001734201122253</v>
+        <v>0.4194787235783255</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1993565395102425</v>
+        <v>0.2012565395102425</v>
       </c>
       <c r="C68">
-        <v>-107.3672295703885</v>
+        <v>-111.4996483250333</v>
       </c>
       <c r="D68">
-        <v>82.1807704296115</v>
+        <v>81.17635167496674</v>
       </c>
       <c r="E68">
-        <v>119.648</v>
+        <v>122.776</v>
       </c>
       <c r="F68">
-        <v>206.448</v>
+        <v>209.576</v>
       </c>
       <c r="G68">
         <v>16.9</v>
@@ -6991,37 +6991,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M68">
-        <v>48.68043840000001</v>
+        <v>49.41802080000001</v>
       </c>
       <c r="N68">
-        <v>-28.2600302367347</v>
+        <v>-28.9976126367347</v>
       </c>
       <c r="O68">
-        <v>-5.652006047346941</v>
+        <v>-5.799522527346941</v>
       </c>
       <c r="P68">
-        <v>-22.60802418938776</v>
+        <v>-23.19809010938776</v>
       </c>
       <c r="Q68">
-        <v>-12.00802418938776</v>
+        <v>-12.59809010938776</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1670149013789766</v>
+        <v>0.1706880802086425</v>
       </c>
       <c r="T68">
-        <v>2.362704045053545</v>
+        <v>2.434301137327895</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.08389574471566512</v>
+        <v>0.08264356942140146</v>
       </c>
       <c r="W68">
-        <v>0.2160173833960462</v>
+        <v>0.2163126463304335</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4194787235783255</v>
+        <v>0.4132178471070073</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2012565395102425</v>
+        <v>0.2031565395102425</v>
       </c>
       <c r="C69">
-        <v>-111.4996483250333</v>
+        <v>-115.607811390785</v>
       </c>
       <c r="D69">
-        <v>81.17635167496674</v>
+        <v>80.19618860921503</v>
       </c>
       <c r="E69">
-        <v>122.776</v>
+        <v>125.904</v>
       </c>
       <c r="F69">
-        <v>209.576</v>
+        <v>212.704</v>
       </c>
       <c r="G69">
         <v>16.9</v>
@@ -7073,37 +7073,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M69">
-        <v>49.41802080000001</v>
+        <v>50.15560320000001</v>
       </c>
       <c r="N69">
-        <v>-28.9976126367347</v>
+        <v>-29.7351950367347</v>
       </c>
       <c r="O69">
-        <v>-5.799522527346941</v>
+        <v>-5.947039007346941</v>
       </c>
       <c r="P69">
-        <v>-23.19809010938776</v>
+        <v>-23.78815602938776</v>
       </c>
       <c r="Q69">
-        <v>-12.59809010938776</v>
+        <v>-13.18815602938776</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1706880802086425</v>
+        <v>0.1745908327151626</v>
       </c>
       <c r="T69">
-        <v>2.434301137327895</v>
+        <v>2.510373047869392</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.08264356942140146</v>
+        <v>0.0814282228122632</v>
       </c>
       <c r="W69">
-        <v>0.2163126463304335</v>
+        <v>0.2165992250608684</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4132178471070073</v>
+        <v>0.4071411140613159</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2031565395102425</v>
+        <v>0.2050565395102426</v>
       </c>
       <c r="C70">
-        <v>-115.607811390785</v>
+        <v>-119.6925869104974</v>
       </c>
       <c r="D70">
-        <v>80.19618860921503</v>
+        <v>79.23941308950263</v>
       </c>
       <c r="E70">
-        <v>125.904</v>
+        <v>129.032</v>
       </c>
       <c r="F70">
-        <v>212.704</v>
+        <v>215.832</v>
       </c>
       <c r="G70">
         <v>16.9</v>
@@ -7155,37 +7155,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M70">
-        <v>50.15560320000001</v>
+        <v>50.89318560000001</v>
       </c>
       <c r="N70">
-        <v>-29.7351950367347</v>
+        <v>-30.4727774367347</v>
       </c>
       <c r="O70">
-        <v>-5.947039007346941</v>
+        <v>-6.094555487346941</v>
       </c>
       <c r="P70">
-        <v>-23.78815602938776</v>
+        <v>-24.37822194938776</v>
       </c>
       <c r="Q70">
-        <v>-13.18815602938776</v>
+        <v>-13.77822194938776</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1745908327151626</v>
+        <v>0.1787453757059743</v>
       </c>
       <c r="T70">
-        <v>2.510373047869392</v>
+        <v>2.591352823607114</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0814282228122632</v>
+        <v>0.08024810364107098</v>
       </c>
       <c r="W70">
-        <v>0.2165992250608684</v>
+        <v>0.2168774971614355</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4071411140613159</v>
+        <v>0.4012405182053549</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2050565395102426</v>
+        <v>0.2069565395102425</v>
       </c>
       <c r="C71">
-        <v>-119.6925869104974</v>
+        <v>-123.7548020861744</v>
       </c>
       <c r="D71">
-        <v>79.23941308950263</v>
+        <v>78.30519791382567</v>
       </c>
       <c r="E71">
-        <v>129.032</v>
+        <v>132.16</v>
       </c>
       <c r="F71">
-        <v>215.832</v>
+        <v>218.96</v>
       </c>
       <c r="G71">
         <v>16.9</v>
@@ -7237,37 +7237,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M71">
-        <v>50.89318560000001</v>
+        <v>51.63076800000001</v>
       </c>
       <c r="N71">
-        <v>-30.4727774367347</v>
+        <v>-31.2103598367347</v>
       </c>
       <c r="O71">
-        <v>-6.094555487346941</v>
+        <v>-6.242071967346941</v>
       </c>
       <c r="P71">
-        <v>-24.37822194938776</v>
+        <v>-24.96828786938776</v>
       </c>
       <c r="Q71">
-        <v>-13.77822194938776</v>
+        <v>-14.36828786938776</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1787453757059743</v>
+        <v>0.1831768882295068</v>
       </c>
       <c r="T71">
-        <v>2.591352823607114</v>
+        <v>2.677731251060684</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08024810364107098</v>
+        <v>0.07910170216048425</v>
       </c>
       <c r="W71">
-        <v>0.2168774971614355</v>
+        <v>0.2171478186305578</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4012405182053549</v>
+        <v>0.3955085108024212</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069565395102425</v>
+        <v>0.2088565395102425</v>
       </c>
       <c r="C72">
-        <v>-123.7548020861744</v>
+        <v>-127.7952455642657</v>
       </c>
       <c r="D72">
-        <v>78.30519791382567</v>
+        <v>77.3927544357343</v>
       </c>
       <c r="E72">
-        <v>132.16</v>
+        <v>135.288</v>
       </c>
       <c r="F72">
-        <v>218.96</v>
+        <v>222.088</v>
       </c>
       <c r="G72">
         <v>16.9</v>
@@ -7319,37 +7319,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M72">
-        <v>51.63076800000001</v>
+        <v>52.3683504</v>
       </c>
       <c r="N72">
-        <v>-31.2103598367347</v>
+        <v>-31.9479422367347</v>
       </c>
       <c r="O72">
-        <v>-6.242071967346941</v>
+        <v>-6.38958844734694</v>
       </c>
       <c r="P72">
-        <v>-24.96828786938776</v>
+        <v>-25.55835378938776</v>
       </c>
       <c r="Q72">
-        <v>-14.36828786938776</v>
+        <v>-14.95835378938776</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1831768882295068</v>
+        <v>0.1879140223063864</v>
       </c>
       <c r="T72">
-        <v>2.677731251060684</v>
+        <v>2.770066811442088</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07910170216048425</v>
+        <v>0.07798759367935067</v>
       </c>
       <c r="W72">
-        <v>0.2171478186305578</v>
+        <v>0.2174105254104091</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3955085108024212</v>
+        <v>0.3899379683967533</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2088565395102425</v>
+        <v>0.2107565395102425</v>
       </c>
       <c r="C73">
-        <v>-127.7952455642657</v>
+        <v>-131.8146696561172</v>
       </c>
       <c r="D73">
-        <v>77.3927544357343</v>
+        <v>76.50133034388276</v>
       </c>
       <c r="E73">
-        <v>135.288</v>
+        <v>138.416</v>
       </c>
       <c r="F73">
-        <v>222.088</v>
+        <v>225.216</v>
       </c>
       <c r="G73">
         <v>16.9</v>
@@ -7401,37 +7401,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M73">
-        <v>52.3683504</v>
+        <v>53.10593280000001</v>
       </c>
       <c r="N73">
-        <v>-31.9479422367347</v>
+        <v>-32.6855246367347</v>
       </c>
       <c r="O73">
-        <v>-6.38958844734694</v>
+        <v>-6.53710492734694</v>
       </c>
       <c r="P73">
-        <v>-25.55835378938776</v>
+        <v>-26.14841970938776</v>
       </c>
       <c r="Q73">
-        <v>-14.95835378938776</v>
+        <v>-15.54841970938776</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1879140223063863</v>
+        <v>0.192989523103043</v>
       </c>
       <c r="T73">
-        <v>2.770066811442087</v>
+        <v>2.868997768993589</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07798759367935067</v>
+        <v>0.07690443265602637</v>
       </c>
       <c r="W73">
-        <v>0.2174105254104091</v>
+        <v>0.217665934779709</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3899379683967533</v>
+        <v>0.3845221632801318</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2107565395102425</v>
+        <v>0.2126565395102425</v>
       </c>
       <c r="C74">
-        <v>-131.8146696561172</v>
+        <v>-135.813792406715</v>
       </c>
       <c r="D74">
-        <v>76.50133034388276</v>
+        <v>75.63020759328502</v>
       </c>
       <c r="E74">
-        <v>138.416</v>
+        <v>141.544</v>
       </c>
       <c r="F74">
-        <v>225.216</v>
+        <v>228.344</v>
       </c>
       <c r="G74">
         <v>16.9</v>
@@ -7483,37 +7483,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M74">
-        <v>53.10593280000001</v>
+        <v>53.8435152</v>
       </c>
       <c r="N74">
-        <v>-32.6855246367347</v>
+        <v>-33.42310703673469</v>
       </c>
       <c r="O74">
-        <v>-6.53710492734694</v>
+        <v>-6.684621407346938</v>
       </c>
       <c r="P74">
-        <v>-26.14841970938776</v>
+        <v>-26.73848562938775</v>
       </c>
       <c r="Q74">
-        <v>-15.54841970938776</v>
+        <v>-16.13848562938776</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.192989523103043</v>
+        <v>0.1984409869216742</v>
       </c>
       <c r="T74">
-        <v>2.868997768993589</v>
+        <v>2.975256945622982</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07690443265602637</v>
+        <v>0.07585094727717669</v>
       </c>
       <c r="W74">
-        <v>0.217665934779709</v>
+        <v>0.2179143466320418</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3845221632801318</v>
+        <v>0.3792547363858835</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2126565395102425</v>
+        <v>0.2145565395102425</v>
       </c>
       <c r="C75">
-        <v>-135.813792406715</v>
+        <v>-139.7932995236793</v>
       </c>
       <c r="D75">
-        <v>75.63020759328502</v>
+        <v>74.77870047632069</v>
       </c>
       <c r="E75">
-        <v>141.544</v>
+        <v>144.672</v>
       </c>
       <c r="F75">
-        <v>228.344</v>
+        <v>231.472</v>
       </c>
       <c r="G75">
         <v>16.9</v>
@@ -7565,37 +7565,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M75">
-        <v>53.8435152</v>
+        <v>54.58109760000001</v>
       </c>
       <c r="N75">
-        <v>-33.42310703673469</v>
+        <v>-34.1606894367347</v>
       </c>
       <c r="O75">
-        <v>-6.684621407346938</v>
+        <v>-6.83213788734694</v>
       </c>
       <c r="P75">
-        <v>-26.73848562938775</v>
+        <v>-27.32855154938776</v>
       </c>
       <c r="Q75">
-        <v>-16.13848562938776</v>
+        <v>-16.72855154938776</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1984409869216742</v>
+        <v>0.2043117941109694</v>
       </c>
       <c r="T75">
-        <v>2.975256945622982</v>
+        <v>3.08968990507002</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07585094727717669</v>
+        <v>0.07482593447613375</v>
       </c>
       <c r="W75">
-        <v>0.2179143466320418</v>
+        <v>0.2181560446505277</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3792547363858835</v>
+        <v>0.3741296723806687</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2145565395102425</v>
+        <v>0.2164565395102425</v>
       </c>
       <c r="C76">
-        <v>-139.7932995236793</v>
+        <v>-143.7538461774012</v>
       </c>
       <c r="D76">
-        <v>74.77870047632069</v>
+        <v>73.9461538225988</v>
       </c>
       <c r="E76">
-        <v>144.672</v>
+        <v>147.8</v>
       </c>
       <c r="F76">
-        <v>231.472</v>
+        <v>234.6</v>
       </c>
       <c r="G76">
         <v>16.9</v>
@@ -7647,37 +7647,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M76">
-        <v>54.58109760000001</v>
+        <v>55.31868000000001</v>
       </c>
       <c r="N76">
-        <v>-34.1606894367347</v>
+        <v>-34.8982718367347</v>
       </c>
       <c r="O76">
-        <v>-6.83213788734694</v>
+        <v>-6.97965436734694</v>
       </c>
       <c r="P76">
-        <v>-27.32855154938776</v>
+        <v>-27.91861746938776</v>
       </c>
       <c r="Q76">
-        <v>-16.72855154938776</v>
+        <v>-17.31861746938776</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2043117941109694</v>
+        <v>0.2106522658754081</v>
       </c>
       <c r="T76">
-        <v>3.08968990507002</v>
+        <v>3.213277501272821</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.07482593447613375</v>
+        <v>0.07382825534978531</v>
       </c>
       <c r="W76">
-        <v>0.2181560446505277</v>
+        <v>0.2183912973885206</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3741296723806687</v>
+        <v>0.3691412767489265</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2164565395102425</v>
+        <v>0.2183565395102425</v>
       </c>
       <c r="C77">
-        <v>-143.7538461774012</v>
+        <v>-147.6960586822515</v>
       </c>
       <c r="D77">
-        <v>73.9461538225988</v>
+        <v>73.13194131774851</v>
       </c>
       <c r="E77">
-        <v>147.8</v>
+        <v>150.928</v>
       </c>
       <c r="F77">
-        <v>234.6</v>
+        <v>237.728</v>
       </c>
       <c r="G77">
         <v>16.9</v>
@@ -7729,37 +7729,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M77">
-        <v>55.31868000000001</v>
+        <v>56.0562624</v>
       </c>
       <c r="N77">
-        <v>-34.8982718367347</v>
+        <v>-35.63585423673469</v>
       </c>
       <c r="O77">
-        <v>-6.97965436734694</v>
+        <v>-7.127170847346939</v>
       </c>
       <c r="P77">
-        <v>-27.91861746938776</v>
+        <v>-28.50868338938776</v>
       </c>
       <c r="Q77">
-        <v>-17.31861746938776</v>
+        <v>-17.90868338938776</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2106522658754081</v>
+        <v>0.2175211102868835</v>
       </c>
       <c r="T77">
-        <v>3.213277501272821</v>
+        <v>3.347164063825855</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.07382825534978531</v>
+        <v>0.07285683093728813</v>
       </c>
       <c r="W77">
-        <v>0.2183912973885206</v>
+        <v>0.2186203592649875</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3691412767489265</v>
+        <v>0.3642841546864406</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2183565395102425</v>
+        <v>0.2202565395102425</v>
       </c>
       <c r="C78">
-        <v>-147.6960586822515</v>
+        <v>-151.6205360679305</v>
       </c>
       <c r="D78">
-        <v>73.13194131774851</v>
+        <v>72.33546393206947</v>
       </c>
       <c r="E78">
-        <v>150.928</v>
+        <v>154.056</v>
       </c>
       <c r="F78">
-        <v>237.728</v>
+        <v>240.856</v>
       </c>
       <c r="G78">
         <v>16.9</v>
@@ -7811,37 +7811,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M78">
-        <v>56.0562624</v>
+        <v>56.79384480000001</v>
       </c>
       <c r="N78">
-        <v>-35.63585423673469</v>
+        <v>-36.3734366367347</v>
       </c>
       <c r="O78">
-        <v>-7.127170847346939</v>
+        <v>-7.274687327346941</v>
       </c>
       <c r="P78">
-        <v>-28.50868338938776</v>
+        <v>-29.09874930938776</v>
       </c>
       <c r="Q78">
-        <v>-17.90868338938776</v>
+        <v>-18.49874930938777</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2175211102868835</v>
+        <v>0.224987245516748</v>
       </c>
       <c r="T78">
-        <v>3.347164063825855</v>
+        <v>3.49269293616611</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07285683093728813</v>
+        <v>0.07191063832771295</v>
       </c>
       <c r="W78">
-        <v>0.2186203592649875</v>
+        <v>0.2188434714823253</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3642841546864406</v>
+        <v>0.3595531916385647</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2202565395102425</v>
+        <v>0.2221565395102425</v>
       </c>
       <c r="C79">
-        <v>-151.6205360679305</v>
+        <v>-155.5278515492424</v>
       </c>
       <c r="D79">
-        <v>72.33546393206947</v>
+        <v>71.55614845075758</v>
       </c>
       <c r="E79">
-        <v>154.056</v>
+        <v>157.184</v>
       </c>
       <c r="F79">
-        <v>240.856</v>
+        <v>243.984</v>
       </c>
       <c r="G79">
         <v>16.9</v>
@@ -7893,37 +7893,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M79">
-        <v>56.79384480000001</v>
+        <v>57.5314272</v>
       </c>
       <c r="N79">
-        <v>-36.3734366367347</v>
+        <v>-37.1110190367347</v>
       </c>
       <c r="O79">
-        <v>-7.274687327346941</v>
+        <v>-7.422203807346939</v>
       </c>
       <c r="P79">
-        <v>-29.09874930938776</v>
+        <v>-29.68881522938776</v>
       </c>
       <c r="Q79">
-        <v>-18.49874930938777</v>
+        <v>-19.08881522938776</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.224987245516748</v>
+        <v>0.2331321203129638</v>
       </c>
       <c r="T79">
-        <v>3.49269293616611</v>
+        <v>3.651451705991842</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07191063832771295</v>
+        <v>0.07098870706710125</v>
       </c>
       <c r="W79">
-        <v>0.2188434714823253</v>
+        <v>0.2190608628735775</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3595531916385647</v>
+        <v>0.3549435353355063</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2221565395102425</v>
+        <v>0.2240565395102425</v>
       </c>
       <c r="C80">
-        <v>-155.5278515492424</v>
+        <v>-159.4185539018741</v>
       </c>
       <c r="D80">
-        <v>71.55614845075758</v>
+        <v>70.7934460981259</v>
       </c>
       <c r="E80">
-        <v>157.184</v>
+        <v>160.312</v>
       </c>
       <c r="F80">
-        <v>243.984</v>
+        <v>247.112</v>
       </c>
       <c r="G80">
         <v>16.9</v>
@@ -7975,37 +7975,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M80">
-        <v>57.5314272</v>
+        <v>58.26900960000001</v>
       </c>
       <c r="N80">
-        <v>-37.1110190367347</v>
+        <v>-37.8486014367347</v>
       </c>
       <c r="O80">
-        <v>-7.422203807346939</v>
+        <v>-7.569720287346941</v>
       </c>
       <c r="P80">
-        <v>-29.68881522938776</v>
+        <v>-30.27888114938776</v>
       </c>
       <c r="Q80">
-        <v>-19.08881522938776</v>
+        <v>-19.67888114938777</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2331321203129638</v>
+        <v>0.242052697470724</v>
       </c>
       <c r="T80">
-        <v>3.651451705991842</v>
+        <v>3.825330358658121</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07098870706710125</v>
+        <v>0.07009011583840376</v>
       </c>
       <c r="W80">
-        <v>0.2190608628735775</v>
+        <v>0.2192727506853044</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3549435353355063</v>
+        <v>0.3504505791920188</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2240565395102425</v>
+        <v>0.2259565395102425</v>
       </c>
       <c r="C81">
-        <v>-159.4185539018741</v>
+        <v>-163.2931687511163</v>
       </c>
       <c r="D81">
-        <v>70.7934460981259</v>
+        <v>70.04683124888369</v>
       </c>
       <c r="E81">
-        <v>160.312</v>
+        <v>163.44</v>
       </c>
       <c r="F81">
-        <v>247.112</v>
+        <v>250.24</v>
       </c>
       <c r="G81">
         <v>16.9</v>
@@ -8057,37 +8057,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M81">
-        <v>58.26900960000001</v>
+        <v>59.006592</v>
       </c>
       <c r="N81">
-        <v>-37.8486014367347</v>
+        <v>-38.5861838367347</v>
       </c>
       <c r="O81">
-        <v>-7.569720287346941</v>
+        <v>-7.71723676734694</v>
       </c>
       <c r="P81">
-        <v>-30.27888114938776</v>
+        <v>-30.86894706938776</v>
       </c>
       <c r="Q81">
-        <v>-19.67888114938777</v>
+        <v>-20.26894706938776</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.242052697470724</v>
+        <v>0.2518653323442602</v>
       </c>
       <c r="T81">
-        <v>3.825330358658121</v>
+        <v>4.016596876591027</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07009011583840376</v>
+        <v>0.06921398939042371</v>
       </c>
       <c r="W81">
-        <v>0.2192727506853044</v>
+        <v>0.2194793413017381</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3504505791920188</v>
+        <v>0.3460699469521186</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2259565395102425</v>
+        <v>0.2278565395102425</v>
       </c>
       <c r="C82">
-        <v>-163.2931687511163</v>
+        <v>-167.1521997798885</v>
       </c>
       <c r="D82">
-        <v>70.04683124888369</v>
+        <v>69.3158002201115</v>
       </c>
       <c r="E82">
-        <v>163.44</v>
+        <v>166.568</v>
       </c>
       <c r="F82">
-        <v>250.24</v>
+        <v>253.368</v>
       </c>
       <c r="G82">
         <v>16.9</v>
@@ -8139,37 +8139,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M82">
-        <v>59.006592</v>
+        <v>59.74417440000001</v>
       </c>
       <c r="N82">
-        <v>-38.5861838367347</v>
+        <v>-39.3237662367347</v>
       </c>
       <c r="O82">
-        <v>-7.71723676734694</v>
+        <v>-7.86475324734694</v>
       </c>
       <c r="P82">
-        <v>-30.86894706938776</v>
+        <v>-31.45901298938776</v>
       </c>
       <c r="Q82">
-        <v>-20.26894706938776</v>
+        <v>-20.85901298938776</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2518653323442602</v>
+        <v>0.2627108761518528</v>
       </c>
       <c r="T82">
-        <v>4.016596876591027</v>
+        <v>4.227996712201081</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06921398939042371</v>
+        <v>0.06835949569424564</v>
       </c>
       <c r="W82">
-        <v>0.2194793413017381</v>
+        <v>0.2196808309152969</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3460699469521186</v>
+        <v>0.3417974784712282</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2278565395102425</v>
+        <v>0.2297565395102425</v>
       </c>
       <c r="C83">
-        <v>-167.1521997798885</v>
+        <v>-170.9961298619006</v>
       </c>
       <c r="D83">
-        <v>69.3158002201115</v>
+        <v>68.59987013809949</v>
       </c>
       <c r="E83">
-        <v>166.568</v>
+        <v>169.696</v>
       </c>
       <c r="F83">
-        <v>253.368</v>
+        <v>256.496</v>
       </c>
       <c r="G83">
         <v>16.9</v>
@@ -8221,37 +8221,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M83">
-        <v>59.74417440000001</v>
+        <v>60.48175680000001</v>
       </c>
       <c r="N83">
-        <v>-39.3237662367347</v>
+        <v>-40.06134863673471</v>
       </c>
       <c r="O83">
-        <v>-7.86475324734694</v>
+        <v>-8.012269727346942</v>
       </c>
       <c r="P83">
-        <v>-31.45901298938776</v>
+        <v>-32.04907890938777</v>
       </c>
       <c r="Q83">
-        <v>-20.85901298938776</v>
+        <v>-21.44907890938777</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2627108761518528</v>
+        <v>0.2747614803825114</v>
       </c>
       <c r="T83">
-        <v>4.227996712201081</v>
+        <v>4.462885418434475</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06835949569424564</v>
+        <v>0.06752584330773045</v>
       </c>
       <c r="W83">
-        <v>0.2196808309152969</v>
+        <v>0.2198774061480372</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3417974784712282</v>
+        <v>0.3376292165386522</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2297565395102425</v>
+        <v>0.2316565395102425</v>
       </c>
       <c r="C84">
-        <v>-170.9961298619006</v>
+        <v>-174.8254221253089</v>
       </c>
       <c r="D84">
-        <v>68.59987013809949</v>
+        <v>67.89857787469111</v>
       </c>
       <c r="E84">
-        <v>169.696</v>
+        <v>172.824</v>
       </c>
       <c r="F84">
-        <v>256.496</v>
+        <v>259.624</v>
       </c>
       <c r="G84">
         <v>16.9</v>
@@ -8303,37 +8303,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M84">
-        <v>60.48175680000001</v>
+        <v>61.21933920000001</v>
       </c>
       <c r="N84">
-        <v>-40.06134863673471</v>
+        <v>-40.7989310367347</v>
       </c>
       <c r="O84">
-        <v>-8.012269727346942</v>
+        <v>-8.15978620734694</v>
       </c>
       <c r="P84">
-        <v>-32.04907890938777</v>
+        <v>-32.63914482938776</v>
       </c>
       <c r="Q84">
-        <v>-21.44907890938777</v>
+        <v>-22.03914482938776</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2747614803825114</v>
+        <v>0.2882298027579532</v>
       </c>
       <c r="T84">
-        <v>4.462885418434475</v>
+        <v>4.725408090107091</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06752584330773045</v>
+        <v>0.06671227893052888</v>
       </c>
       <c r="W84">
-        <v>0.2198774061480372</v>
+        <v>0.2200692446281813</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3376292165386522</v>
+        <v>0.3335613946526444</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2316565395102425</v>
+        <v>0.2335565395102425</v>
       </c>
       <c r="C85">
-        <v>-174.8254221253089</v>
+        <v>-178.6405209517915</v>
       </c>
       <c r="D85">
-        <v>67.89857787469111</v>
+        <v>67.21147904820855</v>
       </c>
       <c r="E85">
-        <v>172.824</v>
+        <v>175.952</v>
       </c>
       <c r="F85">
-        <v>259.624</v>
+        <v>262.752</v>
       </c>
       <c r="G85">
         <v>16.9</v>
@@ -8385,37 +8385,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M85">
-        <v>61.21933920000001</v>
+        <v>61.95692160000001</v>
       </c>
       <c r="N85">
-        <v>-40.7989310367347</v>
+        <v>-41.5365134367347</v>
       </c>
       <c r="O85">
-        <v>-8.15978620734694</v>
+        <v>-8.30730268734694</v>
       </c>
       <c r="P85">
-        <v>-32.63914482938776</v>
+        <v>-33.22921074938776</v>
       </c>
       <c r="Q85">
-        <v>-22.03914482938776</v>
+        <v>-22.62921074938776</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2882298027579532</v>
+        <v>0.3033816654303254</v>
       </c>
       <c r="T85">
-        <v>4.725408090107091</v>
+        <v>5.020746095738786</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06671227893052888</v>
+        <v>0.06591808513373687</v>
       </c>
       <c r="W85">
-        <v>0.2200692446281813</v>
+        <v>0.2202565155254649</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3335613946526444</v>
+        <v>0.3295904256686844</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335565395102425</v>
+        <v>0.2354565395102425</v>
       </c>
       <c r="C86">
-        <v>-178.6405209517915</v>
+        <v>-182.4418529155685</v>
       </c>
       <c r="D86">
-        <v>67.21147904820855</v>
+        <v>66.53814708443147</v>
       </c>
       <c r="E86">
-        <v>175.952</v>
+        <v>179.08</v>
       </c>
       <c r="F86">
-        <v>262.752</v>
+        <v>265.88</v>
       </c>
       <c r="G86">
         <v>16.9</v>
@@ -8467,37 +8467,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M86">
-        <v>61.95692160000001</v>
+        <v>62.694504</v>
       </c>
       <c r="N86">
-        <v>-41.5365134367347</v>
+        <v>-42.27409583673469</v>
       </c>
       <c r="O86">
-        <v>-8.30730268734694</v>
+        <v>-8.454819167346939</v>
       </c>
       <c r="P86">
-        <v>-33.22921074938776</v>
+        <v>-33.81927666938775</v>
       </c>
       <c r="Q86">
-        <v>-22.62921074938776</v>
+        <v>-23.21927666938776</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3033816654303252</v>
+        <v>0.3205537764590136</v>
       </c>
       <c r="T86">
-        <v>5.020746095738781</v>
+        <v>5.355462502121368</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06591808513373687</v>
+        <v>0.06514257824981057</v>
       </c>
       <c r="W86">
-        <v>0.2202565155254649</v>
+        <v>0.2204393800486947</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3295904256686844</v>
+        <v>0.3257128912490528</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2354565395102425</v>
+        <v>0.2373565395102425</v>
       </c>
       <c r="C87">
-        <v>-182.4418529155685</v>
+        <v>-186.229827666541</v>
       </c>
       <c r="D87">
-        <v>66.53814708443147</v>
+        <v>65.87817233345902</v>
       </c>
       <c r="E87">
-        <v>179.08</v>
+        <v>182.208</v>
       </c>
       <c r="F87">
-        <v>265.88</v>
+        <v>269.008</v>
       </c>
       <c r="G87">
         <v>16.9</v>
@@ -8549,37 +8549,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M87">
-        <v>62.694504</v>
+        <v>63.4320864</v>
       </c>
       <c r="N87">
-        <v>-42.27409583673469</v>
+        <v>-43.01167823673469</v>
       </c>
       <c r="O87">
-        <v>-8.454819167346939</v>
+        <v>-8.602335647346939</v>
       </c>
       <c r="P87">
-        <v>-33.81927666938775</v>
+        <v>-34.40934258938775</v>
       </c>
       <c r="Q87">
-        <v>-23.21927666938776</v>
+        <v>-23.80934258938775</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3205537764590136</v>
+        <v>0.3401790462060859</v>
       </c>
       <c r="T87">
-        <v>5.355462502121368</v>
+        <v>5.737995537987179</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06514257824981057</v>
+        <v>0.0643851064096965</v>
       </c>
       <c r="W87">
-        <v>0.2204393800486947</v>
+        <v>0.2206179919085936</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3257128912490528</v>
+        <v>0.3219255320484825</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2373565395102425</v>
+        <v>0.2392565395102425</v>
       </c>
       <c r="C88">
-        <v>-186.229827666541</v>
+        <v>-190.0048387613867</v>
       </c>
       <c r="D88">
-        <v>65.87817233345902</v>
+        <v>65.23116123861337</v>
       </c>
       <c r="E88">
-        <v>182.208</v>
+        <v>185.336</v>
       </c>
       <c r="F88">
-        <v>269.008</v>
+        <v>272.136</v>
       </c>
       <c r="G88">
         <v>16.9</v>
@@ -8631,37 +8631,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M88">
-        <v>63.4320864</v>
+        <v>64.16966880000001</v>
       </c>
       <c r="N88">
-        <v>-43.01167823673469</v>
+        <v>-43.7492606367347</v>
       </c>
       <c r="O88">
-        <v>-8.602335647346939</v>
+        <v>-8.749852127346941</v>
       </c>
       <c r="P88">
-        <v>-34.40934258938775</v>
+        <v>-34.99940850938776</v>
       </c>
       <c r="Q88">
-        <v>-23.80934258938775</v>
+        <v>-24.39940850938777</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3401790462060859</v>
+        <v>0.3628235882219387</v>
       </c>
       <c r="T88">
-        <v>5.737995537987179</v>
+        <v>6.179379810140039</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0643851064096965</v>
+        <v>0.06364504771533215</v>
       </c>
       <c r="W88">
-        <v>0.2206179919085936</v>
+        <v>0.2207924977487247</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3219255320484825</v>
+        <v>0.3182252385766607</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2392565395102425</v>
+        <v>0.2411565395102425</v>
       </c>
       <c r="C89">
-        <v>-190.0048387613867</v>
+        <v>-193.7672644461581</v>
       </c>
       <c r="D89">
-        <v>65.23116123861337</v>
+        <v>64.59673555384194</v>
       </c>
       <c r="E89">
-        <v>185.336</v>
+        <v>188.464</v>
       </c>
       <c r="F89">
-        <v>272.136</v>
+        <v>275.264</v>
       </c>
       <c r="G89">
         <v>16.9</v>
@@ -8713,37 +8713,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M89">
-        <v>64.16966880000001</v>
+        <v>64.9072512</v>
       </c>
       <c r="N89">
-        <v>-43.7492606367347</v>
+        <v>-44.4868430367347</v>
       </c>
       <c r="O89">
-        <v>-8.749852127346941</v>
+        <v>-8.897368607346939</v>
       </c>
       <c r="P89">
-        <v>-34.99940850938776</v>
+        <v>-35.58947442938776</v>
       </c>
       <c r="Q89">
-        <v>-24.39940850938777</v>
+        <v>-24.98947442938776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3628235882219387</v>
+        <v>0.389242220573767</v>
       </c>
       <c r="T89">
-        <v>6.179379810140039</v>
+        <v>6.69432812765171</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06364504771533215</v>
+        <v>0.06292180853674884</v>
       </c>
       <c r="W89">
-        <v>0.2207924977487247</v>
+        <v>0.2209630375470346</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3182252385766607</v>
+        <v>0.3146090426837442</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2411565395102425</v>
+        <v>0.2430565395102425</v>
       </c>
       <c r="C90">
-        <v>-193.7672644461581</v>
+        <v>-197.5174683936522</v>
       </c>
       <c r="D90">
-        <v>64.59673555384194</v>
+        <v>63.97453160634782</v>
       </c>
       <c r="E90">
-        <v>188.464</v>
+        <v>191.592</v>
       </c>
       <c r="F90">
-        <v>275.264</v>
+        <v>278.392</v>
       </c>
       <c r="G90">
         <v>16.9</v>
@@ -8795,37 +8795,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M90">
-        <v>64.9072512</v>
+        <v>65.6448336</v>
       </c>
       <c r="N90">
-        <v>-44.4868430367347</v>
+        <v>-45.22442543673469</v>
       </c>
       <c r="O90">
-        <v>-8.897368607346939</v>
+        <v>-9.044885087346939</v>
       </c>
       <c r="P90">
-        <v>-35.58947442938776</v>
+        <v>-36.17954034938775</v>
       </c>
       <c r="Q90">
-        <v>-24.98947442938776</v>
+        <v>-25.57954034938775</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.389242220573767</v>
+        <v>0.4204642406259276</v>
       </c>
       <c r="T90">
-        <v>6.69432812765171</v>
+        <v>7.302903411983683</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06292180853674884</v>
+        <v>0.06221482192397638</v>
       </c>
       <c r="W90">
-        <v>0.2209630375470346</v>
+        <v>0.2211297449903264</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3146090426837442</v>
+        <v>0.3110741096198819</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430565395102425</v>
+        <v>0.2449565395102425</v>
       </c>
       <c r="C91">
-        <v>-197.5174683936522</v>
+        <v>-201.2558003985714</v>
       </c>
       <c r="D91">
-        <v>63.97453160634782</v>
+        <v>63.3641996014286</v>
       </c>
       <c r="E91">
-        <v>191.592</v>
+        <v>194.72</v>
       </c>
       <c r="F91">
-        <v>278.392</v>
+        <v>281.52</v>
       </c>
       <c r="G91">
         <v>16.9</v>
@@ -8877,37 +8877,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M91">
-        <v>65.6448336</v>
+        <v>66.38241600000001</v>
       </c>
       <c r="N91">
-        <v>-45.22442543673469</v>
+        <v>-45.9620078367347</v>
       </c>
       <c r="O91">
-        <v>-9.044885087346939</v>
+        <v>-9.192401567346939</v>
       </c>
       <c r="P91">
-        <v>-36.17954034938775</v>
+        <v>-36.76960626938776</v>
       </c>
       <c r="Q91">
-        <v>-25.57954034938775</v>
+        <v>-26.16960626938776</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4204642406259276</v>
+        <v>0.4579306646885204</v>
       </c>
       <c r="T91">
-        <v>7.302903411983683</v>
+        <v>8.033193753182053</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06221482192397638</v>
+        <v>0.06152354612482108</v>
       </c>
       <c r="W91">
-        <v>0.2211297449903264</v>
+        <v>0.2212927478237672</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3110741096198819</v>
+        <v>0.3076177306241055</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449565395102425</v>
+        <v>0.2468565395102425</v>
       </c>
       <c r="C92">
-        <v>-201.2558003985714</v>
+        <v>-204.9825970332692</v>
       </c>
       <c r="D92">
-        <v>63.3641996014286</v>
+        <v>62.76540296673081</v>
       </c>
       <c r="E92">
-        <v>194.72</v>
+        <v>197.848</v>
       </c>
       <c r="F92">
-        <v>281.52</v>
+        <v>284.648</v>
       </c>
       <c r="G92">
         <v>16.9</v>
@@ -8959,37 +8959,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M92">
-        <v>66.38241600000001</v>
+        <v>67.11999840000001</v>
       </c>
       <c r="N92">
-        <v>-45.9620078367347</v>
+        <v>-46.69959023673471</v>
       </c>
       <c r="O92">
-        <v>-9.192401567346939</v>
+        <v>-9.339918047346941</v>
       </c>
       <c r="P92">
-        <v>-36.76960626938776</v>
+        <v>-37.35967218938777</v>
       </c>
       <c r="Q92">
-        <v>-26.16960626938776</v>
+        <v>-26.75967218938777</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4579306646885204</v>
+        <v>0.5037229607650228</v>
       </c>
       <c r="T92">
-        <v>8.033193753182053</v>
+        <v>8.925770836868949</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06152354612482108</v>
+        <v>0.06084746320037249</v>
       </c>
       <c r="W92">
-        <v>0.2212927478237672</v>
+        <v>0.2214521681773522</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3076177306241055</v>
+        <v>0.3042373160018624</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468565395102425</v>
+        <v>0.2487565395102425</v>
       </c>
       <c r="C93">
-        <v>-204.9825970332692</v>
+        <v>-208.6981822666623</v>
       </c>
       <c r="D93">
-        <v>62.76540296673081</v>
+        <v>62.17781773333767</v>
       </c>
       <c r="E93">
-        <v>197.848</v>
+        <v>200.976</v>
       </c>
       <c r="F93">
-        <v>284.648</v>
+        <v>287.776</v>
       </c>
       <c r="G93">
         <v>16.9</v>
@@ -9041,37 +9041,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M93">
-        <v>67.11999840000001</v>
+        <v>67.85758080000001</v>
       </c>
       <c r="N93">
-        <v>-46.69959023673471</v>
+        <v>-47.4371726367347</v>
       </c>
       <c r="O93">
-        <v>-9.339918047346941</v>
+        <v>-9.48743452734694</v>
       </c>
       <c r="P93">
-        <v>-37.35967218938777</v>
+        <v>-37.94973810938776</v>
       </c>
       <c r="Q93">
-        <v>-26.75967218938777</v>
+        <v>-27.34973810938776</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5037229607650228</v>
+        <v>0.5609633308606508</v>
       </c>
       <c r="T93">
-        <v>8.925770836868949</v>
+        <v>10.04149219147757</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06084746320037249</v>
+        <v>0.06018607773080323</v>
       </c>
       <c r="W93">
-        <v>0.2214521681773522</v>
+        <v>0.2216081228710766</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3042373160018624</v>
+        <v>0.3009303886540161</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487565395102425</v>
+        <v>0.2506565395102425</v>
       </c>
       <c r="C94">
-        <v>-208.6981822666623</v>
+        <v>-212.4028680487017</v>
       </c>
       <c r="D94">
-        <v>62.17781773333767</v>
+        <v>61.60113195129831</v>
       </c>
       <c r="E94">
-        <v>200.976</v>
+        <v>204.104</v>
       </c>
       <c r="F94">
-        <v>287.776</v>
+        <v>290.9040000000001</v>
       </c>
       <c r="G94">
         <v>16.9</v>
@@ -9123,37 +9123,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M94">
-        <v>67.85758080000001</v>
+        <v>68.59516320000002</v>
       </c>
       <c r="N94">
-        <v>-47.4371726367347</v>
+        <v>-48.17475503673471</v>
       </c>
       <c r="O94">
-        <v>-9.48743452734694</v>
+        <v>-9.634951007346942</v>
       </c>
       <c r="P94">
-        <v>-37.94973810938776</v>
+        <v>-38.53980402938777</v>
       </c>
       <c r="Q94">
-        <v>-27.34973810938776</v>
+        <v>-27.93980402938777</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5609633308606508</v>
+        <v>0.6345580924121723</v>
       </c>
       <c r="T94">
-        <v>10.04149219147757</v>
+        <v>11.47599107597437</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06018607773080323</v>
+        <v>0.05953891560466556</v>
       </c>
       <c r="W94">
-        <v>0.2216081228710766</v>
+        <v>0.2217607237004199</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3009303886540161</v>
+        <v>0.2976945780233278</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506565395102425</v>
+        <v>0.2525565395102425</v>
       </c>
       <c r="C95">
-        <v>-212.4028680487017</v>
+        <v>-216.0969548626168</v>
       </c>
       <c r="D95">
-        <v>61.60113195129831</v>
+        <v>61.03504513738321</v>
       </c>
       <c r="E95">
-        <v>204.104</v>
+        <v>207.232</v>
       </c>
       <c r="F95">
-        <v>290.9040000000001</v>
+        <v>294.032</v>
       </c>
       <c r="G95">
         <v>16.9</v>
@@ -9205,37 +9205,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M95">
-        <v>68.59516320000002</v>
+        <v>69.33274560000001</v>
       </c>
       <c r="N95">
-        <v>-48.17475503673471</v>
+        <v>-48.9123374367347</v>
       </c>
       <c r="O95">
-        <v>-9.634951007346942</v>
+        <v>-9.782467487346942</v>
       </c>
       <c r="P95">
-        <v>-38.53980402938777</v>
+        <v>-39.12986994938776</v>
       </c>
       <c r="Q95">
-        <v>-27.93980402938777</v>
+        <v>-28.52986994938776</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6345580924121723</v>
+        <v>0.7326844411475345</v>
       </c>
       <c r="T95">
-        <v>11.47599107597437</v>
+        <v>13.38865625530343</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05953891560466556</v>
+        <v>0.05890552288546699</v>
       </c>
       <c r="W95">
-        <v>0.2217607237004199</v>
+        <v>0.2219100777036069</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2976945780233278</v>
+        <v>0.294527614427335</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525565395102425</v>
+        <v>0.2544565395102425</v>
       </c>
       <c r="C96">
-        <v>-216.0969548626168</v>
+        <v>-219.7807322469884</v>
       </c>
       <c r="D96">
-        <v>61.03504513738321</v>
+        <v>60.47926775301162</v>
       </c>
       <c r="E96">
-        <v>207.232</v>
+        <v>210.36</v>
       </c>
       <c r="F96">
-        <v>294.032</v>
+        <v>297.16</v>
       </c>
       <c r="G96">
         <v>16.9</v>
@@ -9287,37 +9287,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M96">
-        <v>69.33274560000001</v>
+        <v>70.070328</v>
       </c>
       <c r="N96">
-        <v>-48.9123374367347</v>
+        <v>-49.6499198367347</v>
       </c>
       <c r="O96">
-        <v>-9.782467487346942</v>
+        <v>-9.92998396734694</v>
       </c>
       <c r="P96">
-        <v>-39.12986994938776</v>
+        <v>-39.71993586938775</v>
       </c>
       <c r="Q96">
-        <v>-28.52986994938776</v>
+        <v>-29.11993586938776</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7326844411475345</v>
+        <v>0.8700613293770418</v>
       </c>
       <c r="T96">
-        <v>13.38865625530343</v>
+        <v>16.06638750636413</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05890552288546699</v>
+        <v>0.05828546474983051</v>
       </c>
       <c r="W96">
-        <v>0.2219100777036069</v>
+        <v>0.22205628741199</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.294527614427335</v>
+        <v>0.2914273237491525</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544565395102425</v>
+        <v>0.2563565395102425</v>
       </c>
       <c r="C97">
-        <v>-219.7807322469884</v>
+        <v>-223.4544792895547</v>
       </c>
       <c r="D97">
-        <v>60.47926775301162</v>
+        <v>59.93352071044526</v>
       </c>
       <c r="E97">
-        <v>210.36</v>
+        <v>213.488</v>
       </c>
       <c r="F97">
-        <v>297.16</v>
+        <v>300.288</v>
       </c>
       <c r="G97">
         <v>16.9</v>
@@ -9369,37 +9369,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M97">
-        <v>70.070328</v>
+        <v>70.80791040000001</v>
       </c>
       <c r="N97">
-        <v>-49.6499198367347</v>
+        <v>-50.3875022367347</v>
       </c>
       <c r="O97">
-        <v>-9.92998396734694</v>
+        <v>-10.07750044734694</v>
       </c>
       <c r="P97">
-        <v>-39.71993586938775</v>
+        <v>-40.31000178938776</v>
       </c>
       <c r="Q97">
-        <v>-29.11993586938776</v>
+        <v>-29.71000178938776</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8700613293770418</v>
+        <v>1.076126661721303</v>
       </c>
       <c r="T97">
-        <v>16.06638750636413</v>
+        <v>20.08298438295517</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05828546474983051</v>
+        <v>0.05767832449201976</v>
       </c>
       <c r="W97">
-        <v>0.22205628741199</v>
+        <v>0.2221994510847817</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2914273237491525</v>
+        <v>0.2883916224600988</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563565395102425</v>
+        <v>0.2582565395102425</v>
       </c>
       <c r="C98">
-        <v>-223.4544792895547</v>
+        <v>-227.1184650945215</v>
       </c>
       <c r="D98">
-        <v>59.93352071044526</v>
+        <v>59.39753490547851</v>
       </c>
       <c r="E98">
-        <v>213.488</v>
+        <v>216.616</v>
       </c>
       <c r="F98">
-        <v>300.288</v>
+        <v>303.416</v>
       </c>
       <c r="G98">
         <v>16.9</v>
@@ -9451,37 +9451,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M98">
-        <v>70.80791040000001</v>
+        <v>71.54549280000001</v>
       </c>
       <c r="N98">
-        <v>-50.3875022367347</v>
+        <v>-51.1250846367347</v>
       </c>
       <c r="O98">
-        <v>-10.07750044734694</v>
+        <v>-10.22501692734694</v>
       </c>
       <c r="P98">
-        <v>-40.31000178938776</v>
+        <v>-40.90006770938776</v>
       </c>
       <c r="Q98">
-        <v>-29.71000178938776</v>
+        <v>-30.30006770938776</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.0761266617213</v>
+        <v>1.419568882295067</v>
       </c>
       <c r="T98">
-        <v>20.08298438295511</v>
+        <v>26.77731251060682</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05767832449201976</v>
+        <v>0.05708370259004019</v>
       </c>
       <c r="W98">
-        <v>0.2221994510847817</v>
+        <v>0.2223396629292685</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2883916224600988</v>
+        <v>0.2854185129502009</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582565395102425</v>
+        <v>0.2601565395102425</v>
       </c>
       <c r="C99">
-        <v>-227.1184650945215</v>
+        <v>-230.7729492250185</v>
       </c>
       <c r="D99">
-        <v>59.39753490547851</v>
+        <v>58.87105077498148</v>
       </c>
       <c r="E99">
-        <v>216.616</v>
+        <v>219.744</v>
       </c>
       <c r="F99">
-        <v>303.416</v>
+        <v>306.544</v>
       </c>
       <c r="G99">
         <v>16.9</v>
@@ -9533,37 +9533,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M99">
-        <v>71.54549280000001</v>
+        <v>72.2830752</v>
       </c>
       <c r="N99">
-        <v>-51.1250846367347</v>
+        <v>-51.86266703673469</v>
       </c>
       <c r="O99">
-        <v>-10.22501692734694</v>
+        <v>-10.37253340734694</v>
       </c>
       <c r="P99">
-        <v>-40.90006770938776</v>
+        <v>-41.49013362938776</v>
       </c>
       <c r="Q99">
-        <v>-30.30006770938776</v>
+        <v>-30.89013362938776</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.419568882295067</v>
+        <v>2.1064533234426</v>
       </c>
       <c r="T99">
-        <v>26.77731251060682</v>
+        <v>40.16596876591022</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05708370259004019</v>
+        <v>0.05650121582891733</v>
       </c>
       <c r="W99">
-        <v>0.2223396629292685</v>
+        <v>0.2224770133075413</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2854185129502009</v>
+        <v>0.2825060791445866</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601565395102425</v>
+        <v>0.2620565395102425</v>
       </c>
       <c r="C100">
-        <v>-230.7729492250185</v>
+        <v>-234.4181821222331</v>
       </c>
       <c r="D100">
-        <v>58.87105077498148</v>
+        <v>58.35381787776696</v>
       </c>
       <c r="E100">
-        <v>219.744</v>
+        <v>222.872</v>
       </c>
       <c r="F100">
-        <v>306.544</v>
+        <v>309.672</v>
       </c>
       <c r="G100">
         <v>16.9</v>
@@ -9615,37 +9615,37 @@
         <v>20.42040816326531</v>
       </c>
       <c r="M100">
-        <v>72.2830752</v>
+        <v>73.02065760000001</v>
       </c>
       <c r="N100">
-        <v>-51.86266703673469</v>
+        <v>-52.6002494367347</v>
       </c>
       <c r="O100">
-        <v>-10.37253340734694</v>
+        <v>-10.52004988734694</v>
       </c>
       <c r="P100">
-        <v>-41.49013362938776</v>
+        <v>-42.08019954938776</v>
       </c>
       <c r="Q100">
-        <v>-30.89013362938776</v>
+        <v>-31.48019954938776</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.1064533234426</v>
+        <v>4.167106646885199</v>
       </c>
       <c r="T100">
-        <v>40.16596876591022</v>
+        <v>80.33193753182044</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05650121582891733</v>
+        <v>0.05593049647711007</v>
       </c>
       <c r="W100">
-        <v>0.2224770133075413</v>
+        <v>0.2226115889306974</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2825060791445866</v>
+        <v>0.2796524823855504</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620565395102425</v>
-      </c>
-      <c r="C101">
-        <v>-234.4181821222331</v>
-      </c>
-      <c r="D101">
-        <v>58.35381787776696</v>
-      </c>
-      <c r="E101">
-        <v>222.872</v>
-      </c>
-      <c r="F101">
-        <v>309.672</v>
-      </c>
-      <c r="G101">
-        <v>16.9</v>
-      </c>
-      <c r="H101">
-        <v>226</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.02040816326531</v>
-      </c>
-      <c r="K101">
-        <v>10.6</v>
-      </c>
-      <c r="L101">
-        <v>20.42040816326531</v>
-      </c>
-      <c r="M101">
-        <v>73.02065760000001</v>
-      </c>
-      <c r="N101">
-        <v>-52.6002494367347</v>
-      </c>
-      <c r="O101">
-        <v>-10.52004988734694</v>
-      </c>
-      <c r="P101">
-        <v>-42.08019954938776</v>
-      </c>
-      <c r="Q101">
-        <v>-31.48019954938776</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.167106646885199</v>
-      </c>
-      <c r="T101">
-        <v>80.33193753182044</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05593049647711007</v>
-      </c>
-      <c r="W101">
-        <v>0.2226115889306974</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2796524823855504</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
